--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -84,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="545">
   <si>
     <t>_id</t>
   </si>
@@ -584,12 +589,18 @@
     <t>25,26,27,28,29,30,31,32,33,34,35,36</t>
   </si>
   <si>
+    <t>青色专属自选</t>
+  </si>
+  <si>
+    <t>4,4,4,4,4,4</t>
+  </si>
+  <si>
+    <t>1301,1302,1303,1304,1305,1306</t>
+  </si>
+  <si>
     <t>粉色专属自选</t>
   </si>
   <si>
-    <t>4,4,4,4,4,4</t>
-  </si>
-  <si>
     <t>1201,1202,1203,1204,1205,1206</t>
   </si>
   <si>
@@ -1524,6 +1535,195 @@
   </si>
   <si>
     <t>2205,2206,2207,2208,2209,2210</t>
+  </si>
+  <si>
+    <t>2041,2042,2043,2044,2045,2046</t>
+  </si>
+  <si>
+    <t>2047,2048,2049,2050,2051</t>
+  </si>
+  <si>
+    <t>2052,2053,2054,2055,2056,2057,2058</t>
+  </si>
+  <si>
+    <t>2059,2060,2061,2062</t>
+  </si>
+  <si>
+    <t>2063,2064,2065,2066,2067,2068</t>
+  </si>
+  <si>
+    <t>2069,2070,2071,2072</t>
+  </si>
+  <si>
+    <t>流光剑法·入圣</t>
+  </si>
+  <si>
+    <t>3001,3002,3003,3004,3005,3006</t>
+  </si>
+  <si>
+    <t>流光剑法·命中</t>
+  </si>
+  <si>
+    <t>3007,3008,3009,3010,3011,3012</t>
+  </si>
+  <si>
+    <t>武神盾·入圣</t>
+  </si>
+  <si>
+    <t>3013,3014,3015,3016,3017,3018</t>
+  </si>
+  <si>
+    <t>武力精通·入圣</t>
+  </si>
+  <si>
+    <t>3019,3020,3021,3022,3023,3024</t>
+  </si>
+  <si>
+    <t>战吼·入圣</t>
+  </si>
+  <si>
+    <t>3025,3026,3027,3028,3029,3030</t>
+  </si>
+  <si>
+    <t>3031,3032,3033,3034,3035,3036</t>
+  </si>
+  <si>
+    <t>裂地斩·入圣</t>
+  </si>
+  <si>
+    <t>3037,3038,3039,3040,3041,3042</t>
+  </si>
+  <si>
+    <t>3043,3044,3045,3046,3047,3048</t>
+  </si>
+  <si>
+    <t>战士之魂·入圣</t>
+  </si>
+  <si>
+    <t>3049,3050,3051,3052,3053,3054</t>
+  </si>
+  <si>
+    <t>剑二十三·入圣</t>
+  </si>
+  <si>
+    <t>3055,3056,3057,3058,3059,3060</t>
+  </si>
+  <si>
+    <t>剑二十三·命中</t>
+  </si>
+  <si>
+    <t>3061,3062,3063,3064,3065,3066</t>
+  </si>
+  <si>
+    <t>落雷术·入圣</t>
+  </si>
+  <si>
+    <t>4001,4002,4003,4004,4005,4006</t>
+  </si>
+  <si>
+    <t>落雷术·命中</t>
+  </si>
+  <si>
+    <t>4007,4008,4009,4010,4011,4012</t>
+  </si>
+  <si>
+    <t>法力盾·入圣</t>
+  </si>
+  <si>
+    <t>4013,4014,4015,4016,4017,4018</t>
+  </si>
+  <si>
+    <t>法术精通·入圣</t>
+  </si>
+  <si>
+    <t>4019,4020,4021,4022,4023,4024</t>
+  </si>
+  <si>
+    <t>4025,4026,4027,4028,4029,4030</t>
+  </si>
+  <si>
+    <t>心灵传送·入圣</t>
+  </si>
+  <si>
+    <t>4031,4032,4033,4034,4035,4036</t>
+  </si>
+  <si>
+    <t>4037,4038,4039,4040,4041,4042</t>
+  </si>
+  <si>
+    <t>分身术·入圣</t>
+  </si>
+  <si>
+    <t>4043,4044,4045,4046,4047,4048</t>
+  </si>
+  <si>
+    <t>法师之魂·入圣</t>
+  </si>
+  <si>
+    <t>4049,4050,4051,4052,4053,4054</t>
+  </si>
+  <si>
+    <t>魔尊附体·入圣</t>
+  </si>
+  <si>
+    <t>4055,4056,4057,4058,4059,4060</t>
+  </si>
+  <si>
+    <t>4061,4062,4063,4064,4065,4066</t>
+  </si>
+  <si>
+    <t>驱魔符·入圣</t>
+  </si>
+  <si>
+    <t>5001,5002,5003,5004,5005,5006</t>
+  </si>
+  <si>
+    <t>驱魔符·命中</t>
+  </si>
+  <si>
+    <t>5007,5008,5009,5010,5011,5012</t>
+  </si>
+  <si>
+    <t>道力盾·入圣</t>
+  </si>
+  <si>
+    <t>5013,5014,5015,5016,5017,5018</t>
+  </si>
+  <si>
+    <t>道力精通·入圣</t>
+  </si>
+  <si>
+    <t>5019,5020,5021,5022,5023,5024</t>
+  </si>
+  <si>
+    <t>隐身道法·入圣</t>
+  </si>
+  <si>
+    <t>5025,5026,5027,5028,5029,5030</t>
+  </si>
+  <si>
+    <t>5031,5032,5033,5034,5035,5036</t>
+  </si>
+  <si>
+    <t>无极道体·入圣</t>
+  </si>
+  <si>
+    <t>5037,5038,5039,5040,5041,5042</t>
+  </si>
+  <si>
+    <t>道士之魂·入圣</t>
+  </si>
+  <si>
+    <t>5043,5044,5045,5046,5047,5048</t>
+  </si>
+  <si>
+    <t>召唤白虎·入圣</t>
+  </si>
+  <si>
+    <t>5049,5050,5051,5052,5053,5054</t>
+  </si>
+  <si>
+    <t>5055,5056,5057,5058,5059,5060</t>
   </si>
 </sst>
 </file>
@@ -2512,7 +2712,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K135"/>
+  <dimension ref="A1:K136"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="4" max="4" width="16.625" customWidth="1"/>
@@ -4212,7 +4412,7 @@
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>166</v>
@@ -4236,14 +4436,14 @@
         <v>141</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="62" customFormat="1" customHeight="1" spans="1:11">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>169</v>
@@ -4258,10 +4458,10 @@
         <v>2</v>
       </c>
       <c r="H62" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="I62" s="8" t="s">
         <v>170</v>
-      </c>
-      <c r="I62" s="8" t="s">
-        <v>171</v>
       </c>
       <c r="J62" s="8" t="s">
         <v>141</v>
@@ -4274,38 +4474,38 @@
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D63" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E63" s="1">
+        <v>1</v>
+      </c>
+      <c r="F63" s="4">
+        <v>0</v>
+      </c>
+      <c r="G63" s="1">
+        <v>2</v>
+      </c>
+      <c r="H63" s="8" t="s">
         <v>172</v>
-      </c>
-      <c r="E63" s="1">
-        <v>1</v>
-      </c>
-      <c r="F63" s="4">
-        <v>0</v>
-      </c>
-      <c r="G63" s="1">
-        <v>2</v>
-      </c>
-      <c r="H63" s="8" t="s">
-        <v>133</v>
       </c>
       <c r="I63" s="8" t="s">
         <v>173</v>
       </c>
       <c r="J63" s="8" t="s">
-        <v>16</v>
+        <v>141</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="64" customFormat="1" customHeight="1" spans="1:11">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>174</v>
@@ -4320,7 +4520,7 @@
         <v>2</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="I64" s="8" t="s">
         <v>175</v>
@@ -4329,14 +4529,14 @@
         <v>16</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="65" customFormat="1" customHeight="1" spans="1:11">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>176</v>
@@ -4351,27 +4551,29 @@
         <v>2</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I65" s="8" t="s">
         <v>177</v>
       </c>
       <c r="J65" s="8" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="K65" s="1" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="66" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
       <c r="C66" s="1">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>178</v>
       </c>
       <c r="E66" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" s="4">
         <v>0</v>
@@ -4380,13 +4582,13 @@
         <v>2</v>
       </c>
       <c r="H66" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="I66" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="I66" s="8" t="s">
-        <v>180</v>
-      </c>
       <c r="J66" s="8" t="s">
-        <v>181</v>
+        <v>91</v>
       </c>
       <c r="K66" s="1" t="s">
         <v>178</v>
@@ -4394,123 +4596,123 @@
     </row>
     <row r="67" customFormat="1" customHeight="1" spans="1:11">
       <c r="C67" s="1">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D67" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E67" s="1">
+        <v>0</v>
+      </c>
+      <c r="F67" s="4">
+        <v>0</v>
+      </c>
+      <c r="G67" s="1">
+        <v>2</v>
+      </c>
+      <c r="H67" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="I67" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="E67" s="1">
-        <v>1</v>
-      </c>
-      <c r="F67" s="4">
-        <v>0</v>
-      </c>
-      <c r="G67" s="1">
-        <v>2</v>
-      </c>
-      <c r="H67" s="8" t="s">
+      <c r="J67" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="I67" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="J67" s="8" t="s">
-        <v>32</v>
-      </c>
       <c r="K67" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="68" customFormat="1" customHeight="1" spans="1:11">
       <c r="C68" s="1">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D68" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E68" s="1">
+        <v>1</v>
+      </c>
+      <c r="F68" s="4">
+        <v>0</v>
+      </c>
+      <c r="G68" s="1">
+        <v>2</v>
+      </c>
+      <c r="H68" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="E68" s="1">
-        <v>1</v>
-      </c>
-      <c r="F68" s="4">
-        <v>0</v>
-      </c>
-      <c r="G68" s="1">
-        <v>2</v>
-      </c>
-      <c r="H68" s="8" t="s">
+      <c r="I68" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="I68" s="8" t="s">
-        <v>187</v>
-      </c>
       <c r="J68" s="8" t="s">
-        <v>91</v>
+        <v>32</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="69" customFormat="1" customHeight="1" spans="1:11">
       <c r="C69" s="1">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D69" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E69" s="1">
+        <v>1</v>
+      </c>
+      <c r="F69" s="4">
+        <v>0</v>
+      </c>
+      <c r="G69" s="1">
+        <v>2</v>
+      </c>
+      <c r="H69" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="E69" s="1">
-        <v>0</v>
-      </c>
-      <c r="F69" s="4">
-        <v>0</v>
-      </c>
-      <c r="G69" s="1">
-        <v>2</v>
-      </c>
-      <c r="H69" s="8" t="s">
+      <c r="I69" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="I69" s="8" t="s">
-        <v>190</v>
-      </c>
       <c r="J69" s="8" t="s">
-        <v>191</v>
+        <v>91</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="70" customFormat="1" customHeight="1" spans="1:11">
       <c r="C70" s="1">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D70" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E70" s="1">
+        <v>0</v>
+      </c>
+      <c r="F70" s="4">
+        <v>0</v>
+      </c>
+      <c r="G70" s="1">
+        <v>2</v>
+      </c>
+      <c r="H70" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="I70" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="E70" s="1">
-        <v>0</v>
-      </c>
-      <c r="F70" s="4">
-        <v>0</v>
-      </c>
-      <c r="G70" s="1">
-        <v>2</v>
-      </c>
-      <c r="H70" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="I70" s="8" t="s">
+      <c r="J70" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="J70" s="8" t="s">
-        <v>181</v>
-      </c>
       <c r="K70" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="71" customFormat="1" customHeight="1" spans="1:11">
       <c r="C71" s="1">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>194</v>
@@ -4525,13 +4727,13 @@
         <v>2</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I71" s="8" t="s">
         <v>195</v>
       </c>
       <c r="J71" s="8" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="K71" s="1" t="s">
         <v>194</v>
@@ -4539,7 +4741,7 @@
     </row>
     <row r="72" customFormat="1" customHeight="1" spans="1:11">
       <c r="C72" s="1">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>196</v>
@@ -4554,13 +4756,13 @@
         <v>2</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="I72" s="8" t="s">
         <v>197</v>
       </c>
       <c r="J72" s="8" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="K72" s="1" t="s">
         <v>196</v>
@@ -4568,7 +4770,7 @@
     </row>
     <row r="73" customFormat="1" customHeight="1" spans="1:11">
       <c r="C73" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>198</v>
@@ -4583,13 +4785,13 @@
         <v>2</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I73" s="8" t="s">
         <v>199</v>
       </c>
       <c r="J73" s="8" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K73" s="1" t="s">
         <v>198</v>
@@ -4597,7 +4799,7 @@
     </row>
     <row r="74" customFormat="1" customHeight="1" spans="1:11">
       <c r="C74" s="1">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>200</v>
@@ -4612,13 +4814,13 @@
         <v>2</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I74" s="8" t="s">
         <v>201</v>
       </c>
       <c r="J74" s="8" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K74" s="1" t="s">
         <v>200</v>
@@ -4626,7 +4828,7 @@
     </row>
     <row r="75" customFormat="1" customHeight="1" spans="1:11">
       <c r="C75" s="1">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>202</v>
@@ -4641,80 +4843,80 @@
         <v>2</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I75" s="8" t="s">
         <v>203</v>
       </c>
       <c r="J75" s="8" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K75" s="1" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="76" ht="14"/>
-    <row r="77" customFormat="1" customHeight="1" spans="1:11">
-      <c r="C77" s="1">
-        <v>106</v>
-      </c>
-      <c r="D77" s="1" t="s">
+    <row r="76" customFormat="1" customHeight="1" spans="1:11">
+      <c r="C76" s="1">
+        <v>105</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="E77" s="1">
-        <v>1</v>
-      </c>
-      <c r="F77" s="4">
-        <v>0</v>
-      </c>
-      <c r="G77" s="1">
-        <v>1</v>
-      </c>
-      <c r="H77" s="8" t="s">
+      <c r="E76" s="1">
+        <v>0</v>
+      </c>
+      <c r="F76" s="4">
+        <v>0</v>
+      </c>
+      <c r="G76" s="1">
+        <v>2</v>
+      </c>
+      <c r="H76" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="I76" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="I77" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="J77" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="K77" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
+      <c r="J76" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="77" ht="14"/>
     <row r="78" customFormat="1" customHeight="1" spans="1:11">
       <c r="C78" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D78" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E78" s="1">
+        <v>1</v>
+      </c>
+      <c r="F78" s="4">
+        <v>0</v>
+      </c>
+      <c r="G78" s="1">
+        <v>1</v>
+      </c>
+      <c r="H78" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="I78" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J78" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="E78" s="1">
-        <v>1</v>
-      </c>
-      <c r="F78" s="4">
-        <v>0</v>
-      </c>
-      <c r="G78" s="1">
-        <v>2</v>
-      </c>
-      <c r="H78" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="I78" s="8" t="s">
+      <c r="K78" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="J78" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="K78" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="79" customFormat="1" customHeight="1" spans="1:11">
       <c r="C79" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>211</v>
@@ -4738,258 +4940,252 @@
         <v>40</v>
       </c>
       <c r="K79" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="80" customFormat="1" customHeight="1" spans="1:11">
+      <c r="C80" s="1">
+        <v>108</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="80" ht="14"/>
-    <row r="81" customFormat="1" customHeight="1" spans="1:11">
-      <c r="C81" s="1">
-        <v>109</v>
-      </c>
-      <c r="D81" s="1" t="s">
+      <c r="E80" s="1">
+        <v>1</v>
+      </c>
+      <c r="F80" s="4">
+        <v>0</v>
+      </c>
+      <c r="G80" s="1">
+        <v>2</v>
+      </c>
+      <c r="H80" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I80" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="E81" s="1">
-        <v>1</v>
-      </c>
-      <c r="F81" s="4">
-        <v>0</v>
-      </c>
-      <c r="G81" s="4">
-        <v>2</v>
-      </c>
-      <c r="H81" s="8" t="s">
+      <c r="J80" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="K80" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="I81" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="J81" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="K81" s="1" t="s">
-        <v>217</v>
-      </c>
-    </row>
+    </row>
+    <row r="81" ht="14"/>
     <row r="82" customFormat="1" customHeight="1" spans="1:11">
       <c r="C82" s="1">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D82" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E82" s="1">
+        <v>1</v>
+      </c>
+      <c r="F82" s="4">
+        <v>0</v>
+      </c>
+      <c r="G82" s="4">
+        <v>2</v>
+      </c>
+      <c r="H82" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="I82" s="8" t="s">
         <v>218</v>
-      </c>
-      <c r="E82" s="1">
-        <v>1</v>
-      </c>
-      <c r="F82" s="4">
-        <v>0</v>
-      </c>
-      <c r="G82" s="4">
-        <v>2</v>
-      </c>
-      <c r="H82" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="I82" s="8" t="s">
-        <v>219</v>
       </c>
       <c r="J82" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="83" customFormat="1" customHeight="1" spans="1:11">
       <c r="C83" s="1">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D83" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E83" s="1">
+        <v>1</v>
+      </c>
+      <c r="F83" s="4">
+        <v>0</v>
+      </c>
+      <c r="G83" s="4">
+        <v>2</v>
+      </c>
+      <c r="H83" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="I83" s="8" t="s">
         <v>221</v>
-      </c>
-      <c r="E83" s="1">
-        <v>1</v>
-      </c>
-      <c r="F83" s="4">
-        <v>0</v>
-      </c>
-      <c r="G83" s="4">
-        <v>2</v>
-      </c>
-      <c r="H83" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="I83" s="8" t="s">
-        <v>222</v>
       </c>
       <c r="J83" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="84" customFormat="1" customHeight="1" spans="1:11">
       <c r="C84" s="1">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D84" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="E84" s="1">
+        <v>1</v>
+      </c>
+      <c r="F84" s="4">
+        <v>0</v>
+      </c>
+      <c r="G84" s="4">
+        <v>2</v>
+      </c>
+      <c r="H84" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="I84" s="8" t="s">
         <v>224</v>
-      </c>
-      <c r="E84" s="1">
-        <v>1</v>
-      </c>
-      <c r="F84" s="4">
-        <v>0</v>
-      </c>
-      <c r="G84" s="4">
-        <v>2</v>
-      </c>
-      <c r="H84" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="I84" s="8" t="s">
-        <v>225</v>
       </c>
       <c r="J84" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="85" customFormat="1" customHeight="1" spans="1:11">
       <c r="C85" s="1">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D85" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E85" s="1">
+        <v>1</v>
+      </c>
+      <c r="F85" s="4">
+        <v>0</v>
+      </c>
+      <c r="G85" s="4">
+        <v>2</v>
+      </c>
+      <c r="H85" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="I85" s="8" t="s">
         <v>227</v>
-      </c>
-      <c r="E85" s="1">
-        <v>1</v>
-      </c>
-      <c r="F85" s="4">
-        <v>0</v>
-      </c>
-      <c r="G85" s="4">
-        <v>2</v>
-      </c>
-      <c r="H85" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="I85" s="8" t="s">
-        <v>228</v>
       </c>
       <c r="J85" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="86" customFormat="1" customHeight="1" spans="1:11">
       <c r="C86" s="1">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D86" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E86" s="1">
+        <v>1</v>
+      </c>
+      <c r="F86" s="4">
+        <v>0</v>
+      </c>
+      <c r="G86" s="4">
+        <v>2</v>
+      </c>
+      <c r="H86" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="I86" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="E86" s="1">
-        <v>1</v>
-      </c>
-      <c r="F86" s="4">
-        <v>0</v>
-      </c>
-      <c r="G86" s="4">
-        <v>2</v>
-      </c>
-      <c r="H86" s="8" t="s">
+      <c r="J86" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="K86" s="1" t="s">
         <v>231</v>
-      </c>
-      <c r="I86" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="J86" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="K86" s="1" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="87" customFormat="1" customHeight="1" spans="1:11">
       <c r="C87" s="1">
+        <v>114</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E87" s="1">
+        <v>1</v>
+      </c>
+      <c r="F87" s="4">
+        <v>0</v>
+      </c>
+      <c r="G87" s="4">
+        <v>2</v>
+      </c>
+      <c r="H87" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="I87" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="J87" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="88" customFormat="1" customHeight="1" spans="1:11">
+      <c r="C88" s="1">
         <v>115</v>
       </c>
-      <c r="D87" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="E87" s="1">
-        <v>1</v>
-      </c>
-      <c r="F87" s="4">
-        <v>0</v>
-      </c>
-      <c r="G87" s="4">
-        <v>2</v>
-      </c>
-      <c r="H87" s="8" t="s">
+      <c r="D88" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E88" s="1">
+        <v>1</v>
+      </c>
+      <c r="F88" s="4">
+        <v>0</v>
+      </c>
+      <c r="G88" s="4">
+        <v>2</v>
+      </c>
+      <c r="H88" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="I87" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="J87" s="8" t="s">
+      <c r="I88" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="J88" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="K87" s="1" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="88" ht="14"/>
-    <row r="89" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A89" s="1" t="s">
+      <c r="K88" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="C89" s="1">
-        <v>118</v>
-      </c>
-      <c r="D89" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="E89" s="1">
-        <v>1</v>
-      </c>
-      <c r="F89" s="4">
-        <v>0</v>
-      </c>
-      <c r="G89" s="4">
-        <v>2</v>
-      </c>
-      <c r="H89" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="I89" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="J89" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="K89" s="4" t="s">
-        <v>237</v>
-      </c>
-    </row>
+    </row>
+    <row r="89" ht="14"/>
     <row r="90" customFormat="1" customHeight="1" spans="1:11">
       <c r="A90" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C90" s="1">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>239</v>
@@ -5004,7 +5200,7 @@
         <v>2</v>
       </c>
       <c r="H90" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I90" s="8" t="s">
         <v>240</v>
@@ -5018,13 +5214,13 @@
     </row>
     <row r="91" customFormat="1" customHeight="1" spans="1:11">
       <c r="A91" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C91" s="1">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D91" s="4" t="s">
         <v>241</v>
@@ -5039,7 +5235,7 @@
         <v>2</v>
       </c>
       <c r="H91" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I91" s="8" t="s">
         <v>242</v>
@@ -5053,13 +5249,13 @@
     </row>
     <row r="92" customFormat="1" customHeight="1" spans="1:11">
       <c r="A92" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C92" s="1">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>243</v>
@@ -5074,7 +5270,7 @@
         <v>2</v>
       </c>
       <c r="H92" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I92" s="8" t="s">
         <v>244</v>
@@ -5088,13 +5284,13 @@
     </row>
     <row r="93" customFormat="1" customHeight="1" spans="1:11">
       <c r="A93" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C93" s="1">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D93" s="4" t="s">
         <v>245</v>
@@ -5109,7 +5305,7 @@
         <v>2</v>
       </c>
       <c r="H93" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I93" s="8" t="s">
         <v>246</v>
@@ -5123,13 +5319,13 @@
     </row>
     <row r="94" customFormat="1" customHeight="1" spans="1:11">
       <c r="A94" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C94" s="1">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D94" s="4" t="s">
         <v>247</v>
@@ -5144,7 +5340,7 @@
         <v>2</v>
       </c>
       <c r="H94" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I94" s="8" t="s">
         <v>248</v>
@@ -5158,15 +5354,15 @@
     </row>
     <row r="95" customFormat="1" customHeight="1" spans="1:11">
       <c r="A95" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C95" s="1">
-        <v>124</v>
-      </c>
-      <c r="D95" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D95" s="4" t="s">
         <v>249</v>
       </c>
       <c r="E95" s="1">
@@ -5179,7 +5375,7 @@
         <v>2</v>
       </c>
       <c r="H95" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I95" s="8" t="s">
         <v>250</v>
@@ -5187,19 +5383,19 @@
       <c r="J95" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="K95" s="1" t="s">
+      <c r="K95" s="4" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="96" customFormat="1" customHeight="1" spans="1:11">
       <c r="A96" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C96" s="1">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>251</v>
@@ -5214,7 +5410,7 @@
         <v>2</v>
       </c>
       <c r="H96" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I96" s="8" t="s">
         <v>252</v>
@@ -5228,13 +5424,13 @@
     </row>
     <row r="97" customFormat="1" customHeight="1" spans="1:11">
       <c r="A97" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C97" s="1">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>253</v>
@@ -5249,7 +5445,7 @@
         <v>2</v>
       </c>
       <c r="H97" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I97" s="8" t="s">
         <v>254</v>
@@ -5263,13 +5459,13 @@
     </row>
     <row r="98" customFormat="1" customHeight="1" spans="1:11">
       <c r="A98" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C98" s="1">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>255</v>
@@ -5284,7 +5480,7 @@
         <v>2</v>
       </c>
       <c r="H98" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I98" s="8" t="s">
         <v>256</v>
@@ -5298,13 +5494,13 @@
     </row>
     <row r="99" customFormat="1" customHeight="1" spans="1:11">
       <c r="A99" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C99" s="1">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>257</v>
@@ -5319,7 +5515,7 @@
         <v>2</v>
       </c>
       <c r="H99" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I99" s="8" t="s">
         <v>258</v>
@@ -5333,13 +5529,13 @@
     </row>
     <row r="100" customFormat="1" customHeight="1" spans="1:11">
       <c r="A100" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C100" s="1">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>259</v>
@@ -5354,7 +5550,7 @@
         <v>2</v>
       </c>
       <c r="H100" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I100" s="8" t="s">
         <v>260</v>
@@ -5368,13 +5564,13 @@
     </row>
     <row r="101" customFormat="1" customHeight="1" spans="1:11">
       <c r="A101" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C101" s="1">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>261</v>
@@ -5389,7 +5585,7 @@
         <v>2</v>
       </c>
       <c r="H101" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I101" s="8" t="s">
         <v>262</v>
@@ -5403,13 +5599,13 @@
     </row>
     <row r="102" customFormat="1" customHeight="1" spans="1:11">
       <c r="A102" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C102" s="1">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>263</v>
@@ -5424,7 +5620,7 @@
         <v>2</v>
       </c>
       <c r="H102" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I102" s="8" t="s">
         <v>264</v>
@@ -5436,51 +5632,51 @@
         <v>263</v>
       </c>
     </row>
-    <row r="103" ht="14"/>
-    <row r="104" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A104" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="C104" s="1">
-        <v>137</v>
-      </c>
-      <c r="D104" s="1" t="s">
+    <row r="103" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A103" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C103" s="1">
+        <v>131</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="E104" s="1">
-        <v>1</v>
-      </c>
-      <c r="F104" s="4">
-        <v>0</v>
-      </c>
-      <c r="G104" s="4">
-        <v>2</v>
-      </c>
-      <c r="H104" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="I104" s="8" t="s">
+      <c r="E103" s="1">
+        <v>1</v>
+      </c>
+      <c r="F103" s="4">
+        <v>0</v>
+      </c>
+      <c r="G103" s="4">
+        <v>2</v>
+      </c>
+      <c r="H103" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="I103" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="J104" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="K104" s="1" t="s">
+      <c r="J103" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="K103" s="1" t="s">
         <v>265</v>
       </c>
     </row>
+    <row r="104" ht="14"/>
     <row r="105" customFormat="1" customHeight="1" spans="1:11">
       <c r="A105" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C105" s="1">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>267</v>
@@ -5495,13 +5691,13 @@
         <v>2</v>
       </c>
       <c r="H105" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="I105" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="I105" s="8" t="s">
-        <v>269</v>
-      </c>
       <c r="J105" s="8" t="s">
-        <v>270</v>
+        <v>40</v>
       </c>
       <c r="K105" s="1" t="s">
         <v>267</v>
@@ -5509,40 +5705,74 @@
     </row>
     <row r="106" customFormat="1" customHeight="1" spans="1:11">
       <c r="A106" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C106" s="1">
+        <v>138</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="E106" s="1">
+        <v>1</v>
+      </c>
+      <c r="F106" s="4">
+        <v>0</v>
+      </c>
+      <c r="G106" s="4">
+        <v>2</v>
+      </c>
+      <c r="H106" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="I106" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="J106" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="K106" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="107" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A107" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C107" s="1">
         <v>139</v>
       </c>
-      <c r="D106" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="E106" s="1">
-        <v>1</v>
-      </c>
-      <c r="F106" s="4">
-        <v>0</v>
-      </c>
-      <c r="G106" s="4">
-        <v>2</v>
-      </c>
-      <c r="H106" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="I106" s="8" t="s">
+      <c r="D107" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E107" s="1">
+        <v>1</v>
+      </c>
+      <c r="F107" s="4">
+        <v>0</v>
+      </c>
+      <c r="G107" s="4">
+        <v>2</v>
+      </c>
+      <c r="H107" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="I107" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="J107" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="J106" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="K106" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="107" ht="14"/>
+      <c r="K107" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
     <row r="108" ht="14"/>
     <row r="109" ht="14"/>
     <row r="110" ht="14"/>
@@ -5551,300 +5781,272 @@
     <row r="113" ht="14"/>
     <row r="114" ht="14"/>
     <row r="115" ht="14"/>
-    <row r="116" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C116" s="1">
-        <v>201</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="E116" s="1">
-        <v>1</v>
-      </c>
-      <c r="F116" s="4">
-        <v>0</v>
-      </c>
-      <c r="G116" s="4">
-        <v>2</v>
-      </c>
-      <c r="H116" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="I116" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="J116" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="K116" s="1" t="s">
-        <v>276</v>
-      </c>
-    </row>
+    <row r="116" ht="14"/>
     <row r="117" customFormat="1" customHeight="1" spans="3:11">
       <c r="C117" s="1">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D117" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E117" s="1">
+        <v>1</v>
+      </c>
+      <c r="F117" s="4">
+        <v>0</v>
+      </c>
+      <c r="G117" s="4">
+        <v>2</v>
+      </c>
+      <c r="H117" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="I117" s="8" t="s">
         <v>277</v>
-      </c>
-      <c r="E117" s="1">
-        <v>1</v>
-      </c>
-      <c r="F117" s="4">
-        <v>0</v>
-      </c>
-      <c r="G117" s="4">
-        <v>2</v>
-      </c>
-      <c r="H117" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="I117" s="8" t="s">
-        <v>278</v>
       </c>
       <c r="J117" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="118" customFormat="1" customHeight="1" spans="3:11">
       <c r="C118" s="1">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D118" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E118" s="1">
+        <v>1</v>
+      </c>
+      <c r="F118" s="4">
+        <v>0</v>
+      </c>
+      <c r="G118" s="4">
+        <v>2</v>
+      </c>
+      <c r="H118" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="I118" s="8" t="s">
         <v>280</v>
-      </c>
-      <c r="E118" s="1">
-        <v>1</v>
-      </c>
-      <c r="F118" s="4">
-        <v>0</v>
-      </c>
-      <c r="G118" s="4">
-        <v>2</v>
-      </c>
-      <c r="H118" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="I118" s="8" t="s">
-        <v>281</v>
       </c>
       <c r="J118" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="119" customFormat="1" customHeight="1" spans="3:11">
       <c r="C119" s="1">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D119" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="E119" s="1">
+        <v>1</v>
+      </c>
+      <c r="F119" s="4">
+        <v>0</v>
+      </c>
+      <c r="G119" s="4">
+        <v>2</v>
+      </c>
+      <c r="H119" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="I119" s="8" t="s">
         <v>283</v>
-      </c>
-      <c r="E119" s="1">
-        <v>1</v>
-      </c>
-      <c r="F119" s="4">
-        <v>0</v>
-      </c>
-      <c r="G119" s="4">
-        <v>2</v>
-      </c>
-      <c r="H119" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="I119" s="8" t="s">
-        <v>284</v>
       </c>
       <c r="J119" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="120" customFormat="1" customHeight="1" spans="3:11">
       <c r="C120" s="1">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D120" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E120" s="1">
+        <v>1</v>
+      </c>
+      <c r="F120" s="4">
+        <v>0</v>
+      </c>
+      <c r="G120" s="4">
+        <v>2</v>
+      </c>
+      <c r="H120" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="I120" s="8" t="s">
         <v>286</v>
-      </c>
-      <c r="E120" s="1">
-        <v>1</v>
-      </c>
-      <c r="F120" s="4">
-        <v>0</v>
-      </c>
-      <c r="G120" s="4">
-        <v>2</v>
-      </c>
-      <c r="H120" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="I120" s="8" t="s">
-        <v>287</v>
       </c>
       <c r="J120" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="121" ht="14"/>
-    <row r="122" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C122" s="1">
-        <v>207</v>
-      </c>
-      <c r="D122" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="121" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C121" s="1">
+        <v>205</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="E122" s="1">
-        <v>1</v>
-      </c>
-      <c r="F122" s="4">
-        <v>0</v>
-      </c>
-      <c r="G122" s="4">
-        <v>2</v>
-      </c>
-      <c r="H122" s="8" t="s">
+      <c r="E121" s="1">
+        <v>1</v>
+      </c>
+      <c r="F121" s="4">
+        <v>0</v>
+      </c>
+      <c r="G121" s="4">
+        <v>2</v>
+      </c>
+      <c r="H121" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="I121" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="I122" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="J122" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="K122" s="1" t="s">
-        <v>292</v>
-      </c>
-    </row>
+      <c r="J121" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K121" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="122" ht="14"/>
     <row r="123" customFormat="1" customHeight="1" spans="3:11">
       <c r="C123" s="1">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D123" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="E123" s="1">
+        <v>1</v>
+      </c>
+      <c r="F123" s="4">
+        <v>0</v>
+      </c>
+      <c r="G123" s="4">
+        <v>2</v>
+      </c>
+      <c r="H123" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="I123" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="J123" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="E123" s="1">
-        <v>1</v>
-      </c>
-      <c r="F123" s="4">
-        <v>0</v>
-      </c>
-      <c r="G123" s="4">
-        <v>2</v>
-      </c>
-      <c r="H123" s="8" t="s">
+      <c r="K123" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="I123" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="J123" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="K123" s="1" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="124" customFormat="1" customHeight="1" spans="3:11">
       <c r="C124" s="1">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D124" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="E124" s="1">
+        <v>1</v>
+      </c>
+      <c r="F124" s="4">
+        <v>0</v>
+      </c>
+      <c r="G124" s="4">
+        <v>2</v>
+      </c>
+      <c r="H124" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="I124" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="E124" s="1">
-        <v>1</v>
-      </c>
-      <c r="F124" s="4">
-        <v>0</v>
-      </c>
-      <c r="G124" s="4">
-        <v>2</v>
-      </c>
-      <c r="H124" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="I124" s="8" t="s">
+      <c r="J124" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K124" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="J124" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="K124" s="1" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="125" customFormat="1" customHeight="1" spans="3:11">
       <c r="C125" s="1">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D125" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="E125" s="1">
+        <v>1</v>
+      </c>
+      <c r="F125" s="4">
+        <v>0</v>
+      </c>
+      <c r="G125" s="4">
+        <v>2</v>
+      </c>
+      <c r="H125" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="I125" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="E125" s="1">
-        <v>1</v>
-      </c>
-      <c r="F125" s="4">
-        <v>0</v>
-      </c>
-      <c r="G125" s="4">
-        <v>2</v>
-      </c>
-      <c r="H125" s="8" t="s">
+      <c r="J125" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="K125" s="1" t="s">
         <v>301</v>
-      </c>
-      <c r="I125" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="J125" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="K125" s="1" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="126" customFormat="1" customHeight="1" spans="3:11">
       <c r="C126" s="1">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D126" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="E126" s="1">
+        <v>1</v>
+      </c>
+      <c r="F126" s="4">
+        <v>0</v>
+      </c>
+      <c r="G126" s="4">
+        <v>2</v>
+      </c>
+      <c r="H126" s="8" t="s">
         <v>303</v>
-      </c>
-      <c r="E126" s="1">
-        <v>1</v>
-      </c>
-      <c r="F126" s="4">
-        <v>0</v>
-      </c>
-      <c r="G126" s="4">
-        <v>2</v>
-      </c>
-      <c r="H126" s="8" t="s">
-        <v>274</v>
       </c>
       <c r="I126" s="8" t="s">
         <v>304</v>
       </c>
       <c r="J126" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="127" customFormat="1" customHeight="1" spans="3:11">
       <c r="C127" s="1">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>305</v>
@@ -5859,96 +6061,96 @@
         <v>2</v>
       </c>
       <c r="H127" s="8" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I127" s="8" t="s">
         <v>306</v>
       </c>
       <c r="J127" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K127" s="1" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="128" ht="14"/>
+    <row r="128" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C128" s="1">
+        <v>212</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="E128" s="1">
+        <v>1</v>
+      </c>
+      <c r="F128" s="4">
+        <v>0</v>
+      </c>
+      <c r="G128" s="4">
+        <v>2</v>
+      </c>
+      <c r="H128" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="I128" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="J128" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="K128" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
     <row r="129" ht="14"/>
-    <row r="130" ht="14" spans="3:11">
-      <c r="C130" s="1">
-        <v>301</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="E130" s="1">
-        <v>1</v>
-      </c>
-      <c r="F130" s="4">
-        <v>0</v>
-      </c>
-      <c r="G130" s="4">
-        <v>2</v>
-      </c>
-      <c r="H130" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="I130" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="J130" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="K130" s="1" t="s">
-        <v>307</v>
-      </c>
-    </row>
+    <row r="130" ht="14"/>
     <row r="131" ht="14" spans="3:11">
       <c r="C131" s="1">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D131" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E131" s="1">
+        <v>1</v>
+      </c>
+      <c r="F131" s="4">
+        <v>0</v>
+      </c>
+      <c r="G131" s="4">
+        <v>2</v>
+      </c>
+      <c r="H131" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="E131" s="1"/>
-      <c r="F131" s="4"/>
-      <c r="G131" s="4"/>
-      <c r="H131" s="1"/>
-      <c r="I131" s="1"/>
-      <c r="J131" s="1"/>
-      <c r="K131" s="1"/>
+      <c r="I131" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="J131" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="K131" s="1" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="132" ht="14" spans="3:11">
       <c r="C132" s="1">
+        <v>302</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="E132" s="1"/>
+      <c r="F132" s="4"/>
+      <c r="G132" s="4"/>
+      <c r="H132" s="1"/>
+      <c r="I132" s="1"/>
+      <c r="J132" s="1"/>
+      <c r="K132" s="1"/>
+    </row>
+    <row r="133" ht="14" spans="3:11">
+      <c r="C133" s="1">
         <v>303</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E132" s="1">
-        <v>1</v>
-      </c>
-      <c r="F132" s="4">
-        <v>0</v>
-      </c>
-      <c r="G132" s="4">
-        <v>2</v>
-      </c>
-      <c r="H132" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="I132" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="J132" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="K132" s="1" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="133" customFormat="1" ht="14" spans="3:11">
-      <c r="C133" s="1">
-        <v>304</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>313</v>
@@ -5963,20 +6165,49 @@
         <v>2</v>
       </c>
       <c r="H133" s="8" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I133" s="8" t="s">
         <v>314</v>
       </c>
       <c r="J133" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K133" s="1" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="134" ht="14"/>
+    <row r="134" customFormat="1" ht="14" spans="3:11">
+      <c r="C134" s="1">
+        <v>304</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="E134" s="1">
+        <v>1</v>
+      </c>
+      <c r="F134" s="4">
+        <v>0</v>
+      </c>
+      <c r="G134" s="4">
+        <v>2</v>
+      </c>
+      <c r="H134" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="I134" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="J134" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="K134" s="1" t="s">
+        <v>315</v>
+      </c>
+    </row>
     <row r="135" ht="14"/>
+    <row r="136" ht="14"/>
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5 H3:K5" errorStyle="warning">
@@ -5995,7 +6226,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B3:L77"/>
+  <dimension ref="B3:L162"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="2"/>
@@ -6102,7 +6333,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -6117,13 +6348,13 @@
         <v>14</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J6" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6131,7 +6362,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -6146,13 +6377,13 @@
         <v>14</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J7" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6160,7 +6391,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -6175,13 +6406,13 @@
         <v>14</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="J8" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6189,7 +6420,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -6204,13 +6435,13 @@
         <v>14</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="J9" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6218,7 +6449,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -6233,13 +6464,13 @@
         <v>14</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6247,7 +6478,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -6262,13 +6493,13 @@
         <v>14</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="J11" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6276,7 +6507,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -6291,13 +6522,13 @@
         <v>14</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6305,7 +6536,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -6320,13 +6551,13 @@
         <v>14</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="J13" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6334,7 +6565,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -6349,13 +6580,13 @@
         <v>14</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="J14" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6363,7 +6594,7 @@
         <v>1010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -6378,13 +6609,13 @@
         <v>14</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6392,7 +6623,7 @@
         <v>1011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -6407,13 +6638,13 @@
         <v>14</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="J16" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6421,7 +6652,7 @@
         <v>1012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -6436,13 +6667,13 @@
         <v>14</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="J17" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6450,7 +6681,7 @@
         <v>1013</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -6465,13 +6696,13 @@
         <v>14</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J18" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6479,7 +6710,7 @@
         <v>1014</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
@@ -6494,13 +6725,13 @@
         <v>14</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="J19" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1"/>
@@ -6509,7 +6740,7 @@
         <v>1101</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -6524,13 +6755,13 @@
         <v>14</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="J21" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6538,7 +6769,7 @@
         <v>1102</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -6553,13 +6784,13 @@
         <v>14</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="J22" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6567,7 +6798,7 @@
         <v>1103</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -6582,13 +6813,13 @@
         <v>14</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="J23" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6596,7 +6827,7 @@
         <v>1104</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -6611,13 +6842,13 @@
         <v>14</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="J24" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6625,7 +6856,7 @@
         <v>1105</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -6640,13 +6871,13 @@
         <v>14</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="J25" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6654,7 +6885,7 @@
         <v>1106</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -6669,13 +6900,13 @@
         <v>14</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="J26" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6683,7 +6914,7 @@
         <v>1107</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -6698,13 +6929,13 @@
         <v>14</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="J27" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6712,7 +6943,7 @@
         <v>1108</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
@@ -6727,13 +6958,13 @@
         <v>14</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="J28" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6741,7 +6972,7 @@
         <v>1109</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -6756,13 +6987,13 @@
         <v>14</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="J29" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6770,7 +7001,7 @@
         <v>1110</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -6785,13 +7016,13 @@
         <v>14</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="J30" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6799,7 +7030,7 @@
         <v>1111</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -6814,13 +7045,13 @@
         <v>14</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="J31" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6828,7 +7059,7 @@
         <v>1112</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -6843,13 +7074,13 @@
         <v>14</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="J32" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="2:12">
@@ -6870,7 +7101,7 @@
         <v>1201</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
@@ -6885,13 +7116,13 @@
         <v>133</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="J34" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="2:12">
@@ -6900,7 +7131,7 @@
         <v>1202</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
@@ -6912,16 +7143,16 @@
         <v>2</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L35" s="2"/>
     </row>
@@ -6931,7 +7162,7 @@
         <v>1203</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E36" s="1">
         <v>1</v>
@@ -6943,16 +7174,16 @@
         <v>2</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="J36" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L36" s="2"/>
     </row>
@@ -6961,7 +7192,7 @@
         <v>1204</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
@@ -6976,13 +7207,13 @@
         <v>133</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="J37" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="2:12">
@@ -6990,7 +7221,7 @@
         <v>1205</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
@@ -7005,13 +7236,13 @@
         <v>167</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="J38" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="2:12">
@@ -7019,7 +7250,7 @@
         <v>1206</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
@@ -7031,16 +7262,16 @@
         <v>2</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="J39" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="2:12">
@@ -7048,7 +7279,7 @@
         <v>2001</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="E41" s="1">
         <v>1</v>
@@ -7060,16 +7291,16 @@
         <v>2</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I41" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="J41" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K41" s="5" t="s">
         <v>411</v>
-      </c>
-      <c r="J41" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="K41" s="5" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="2:12">
@@ -7077,28 +7308,28 @@
         <v>2002</v>
       </c>
       <c r="D42" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="E42" s="1">
+        <v>1</v>
+      </c>
+      <c r="F42" s="4">
+        <v>0</v>
+      </c>
+      <c r="G42" s="1">
+        <v>2</v>
+      </c>
+      <c r="H42" s="8" t="s">
         <v>412</v>
       </c>
-      <c r="E42" s="1">
-        <v>1</v>
-      </c>
-      <c r="F42" s="4">
-        <v>0</v>
-      </c>
-      <c r="G42" s="1">
-        <v>2</v>
-      </c>
-      <c r="H42" s="8" t="s">
-        <v>410</v>
-      </c>
       <c r="I42" s="8" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="J42" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="2:12">
@@ -7106,7 +7337,7 @@
         <v>2003</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E43" s="1">
         <v>1</v>
@@ -7118,16 +7349,16 @@
         <v>2</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="2:12">
@@ -7135,7 +7366,7 @@
         <v>2004</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E44" s="1">
         <v>1</v>
@@ -7147,16 +7378,16 @@
         <v>2</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="2:12">
@@ -7164,7 +7395,7 @@
         <v>2005</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E45" s="1">
         <v>1</v>
@@ -7176,16 +7407,16 @@
         <v>2</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="2:12">
@@ -7193,7 +7424,7 @@
         <v>2006</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E46" s="1">
         <v>1</v>
@@ -7205,16 +7436,16 @@
         <v>2</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="2:12">
@@ -7223,7 +7454,7 @@
         <v>2007</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E47" s="1">
         <v>1</v>
@@ -7235,16 +7466,16 @@
         <v>2</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="J47" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L47" s="2"/>
     </row>
@@ -7254,7 +7485,7 @@
         <v>2008</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E48" s="1">
         <v>1</v>
@@ -7266,16 +7497,16 @@
         <v>2</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="J48" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L48" s="2"/>
     </row>
@@ -7285,7 +7516,7 @@
         <v>2009</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E49" s="1">
         <v>1</v>
@@ -7297,16 +7528,16 @@
         <v>2</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="L49" s="2"/>
     </row>
@@ -7316,7 +7547,7 @@
         <v>2010</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E50" s="1">
         <v>1</v>
@@ -7328,16 +7559,16 @@
         <v>2</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="J50" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="L50" s="2"/>
     </row>
@@ -7347,7 +7578,7 @@
         <v>2011</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E51" s="1">
         <v>1</v>
@@ -7359,16 +7590,16 @@
         <v>2</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="J51" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L51" s="2"/>
     </row>
@@ -7378,7 +7609,7 @@
         <v>2012</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E52" s="1">
         <v>1</v>
@@ -7390,16 +7621,16 @@
         <v>2</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="J52" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="L52" s="2"/>
     </row>
@@ -7421,7 +7652,7 @@
         <v>2013</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E54" s="1">
         <v>1</v>
@@ -7433,16 +7664,16 @@
         <v>2</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="J54" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K54" s="6" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L54" s="2"/>
     </row>
@@ -7452,7 +7683,7 @@
         <v>2014</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E55" s="1">
         <v>1</v>
@@ -7464,16 +7695,16 @@
         <v>2</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="J55" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K55" s="6" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="L55" s="2"/>
     </row>
@@ -7482,7 +7713,7 @@
         <v>2015</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E56" s="1">
         <v>1</v>
@@ -7494,16 +7725,16 @@
         <v>2</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="J56" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K56" s="6" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="2:12">
@@ -7511,7 +7742,7 @@
         <v>2016</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E57" s="1">
         <v>1</v>
@@ -7523,16 +7754,16 @@
         <v>2</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="J57" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K57" s="6" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="2:12">
@@ -7540,7 +7771,7 @@
         <v>2017</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E58" s="1">
         <v>1</v>
@@ -7552,16 +7783,16 @@
         <v>2</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="J58" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K58" s="6" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="2:12">
@@ -7569,7 +7800,7 @@
         <v>2018</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E59" s="1">
         <v>1</v>
@@ -7581,16 +7812,16 @@
         <v>2</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J59" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K59" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="2:12">
@@ -7598,7 +7829,7 @@
         <v>2019</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E60" s="1">
         <v>1</v>
@@ -7610,16 +7841,16 @@
         <v>2</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I60" s="8" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="J60" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K60" s="6" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="2:12">
@@ -7627,7 +7858,7 @@
         <v>2020</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E61" s="1">
         <v>1</v>
@@ -7639,16 +7870,16 @@
         <v>2</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J61" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K61" s="6" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="2:12">
@@ -7656,7 +7887,7 @@
         <v>2021</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E62" s="1">
         <v>1</v>
@@ -7668,16 +7899,16 @@
         <v>2</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I62" s="8" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="J62" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K62" s="6" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="2:12">
@@ -7685,7 +7916,7 @@
         <v>2022</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E63" s="1">
         <v>1</v>
@@ -7697,16 +7928,16 @@
         <v>2</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="J63" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K63" s="6" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="2:12">
@@ -7714,7 +7945,7 @@
         <v>2023</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E64" s="1">
         <v>1</v>
@@ -7726,24 +7957,24 @@
         <v>2</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I64" s="8" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="J64" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K64" s="6" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="65" customHeight="1" spans="3:11">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="2:12">
       <c r="C65" s="1">
         <v>2024</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E65" s="1">
         <v>1</v>
@@ -7755,24 +7986,24 @@
         <v>2</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="J65" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K65" s="6" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="66" customHeight="1" spans="3:11">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="2:12">
       <c r="C66" s="1">
         <v>2025</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E66" s="1">
         <v>1</v>
@@ -7784,19 +8015,19 @@
         <v>2</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I66" s="8" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="J66" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K66" s="6" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="67" customHeight="1" spans="3:11">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="2:12">
       <c r="C67" s="1"/>
       <c r="D67" s="6"/>
       <c r="E67" s="1"/>
@@ -7806,12 +8037,12 @@
       <c r="I67" s="1"/>
       <c r="K67" s="6"/>
     </row>
-    <row r="68" customHeight="1" spans="3:11">
+    <row r="68" customHeight="1" spans="2:12">
       <c r="C68" s="1">
         <v>2026</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E68" s="1">
         <v>1</v>
@@ -7823,24 +8054,24 @@
         <v>2</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I68" s="8" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="J68" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K68" s="6" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="69" customHeight="1" spans="3:11">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="2:12">
       <c r="C69" s="1">
         <v>2027</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E69" s="1">
         <v>1</v>
@@ -7852,24 +8083,24 @@
         <v>2</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="J69" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K69" s="6" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="70" customHeight="1" spans="3:11">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="2:12">
       <c r="C70" s="1">
         <v>2028</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E70" s="1">
         <v>1</v>
@@ -7881,24 +8112,24 @@
         <v>2</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="J70" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K70" s="6" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="71" customHeight="1" spans="3:11">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="2:12">
       <c r="C71" s="1">
         <v>2029</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E71" s="1">
         <v>1</v>
@@ -7910,24 +8141,24 @@
         <v>2</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I71" s="8" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="J71" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K71" s="6" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="72" customHeight="1" spans="3:11">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="2:12">
       <c r="C72" s="1">
         <v>2030</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E72" s="1">
         <v>1</v>
@@ -7939,24 +8170,24 @@
         <v>2</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I72" s="8" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="J72" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K72" s="6" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="73" customHeight="1" spans="3:11">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="2:12">
       <c r="C73" s="1">
         <v>2031</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E73" s="1">
         <v>1</v>
@@ -7968,24 +8199,24 @@
         <v>2</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="J73" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K73" s="6" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="74" customHeight="1" spans="3:11">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="2:12">
       <c r="C74" s="1">
         <v>2032</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E74" s="1">
         <v>1</v>
@@ -7997,24 +8228,24 @@
         <v>2</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I74" s="8" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="J74" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K74" s="6" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="75" customHeight="1" spans="3:11">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="2:12">
       <c r="C75" s="1">
         <v>2033</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E75" s="1">
         <v>1</v>
@@ -8026,24 +8257,24 @@
         <v>2</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="J75" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K75" s="6" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="76" customHeight="1" spans="3:11">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="2:12">
       <c r="C76" s="1">
         <v>2034</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E76" s="1">
         <v>1</v>
@@ -8055,24 +8286,24 @@
         <v>2</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I76" s="8" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="J76" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K76" s="6" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="77" customHeight="1" spans="3:11">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="2:12">
       <c r="C77" s="1">
         <v>2035</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E77" s="1">
         <v>1</v>
@@ -8084,17 +8315,1248 @@
         <v>2</v>
       </c>
       <c r="H77" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="I77" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="J77" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K77" s="6" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="2:12">
+      <c r="C79" s="1">
+        <v>1301</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="E79" s="1">
+        <v>1</v>
+      </c>
+      <c r="F79" s="4">
+        <v>0</v>
+      </c>
+      <c r="G79" s="1">
+        <v>2</v>
+      </c>
+      <c r="H79" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="I79" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="J79" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="80" s="1" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B80" s="2"/>
+      <c r="C80" s="1">
+        <v>1302</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E80" s="1">
+        <v>1</v>
+      </c>
+      <c r="F80" s="4">
+        <v>0</v>
+      </c>
+      <c r="G80" s="1">
+        <v>2</v>
+      </c>
+      <c r="H80" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="I80" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="J80" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="L80" s="2"/>
+    </row>
+    <row r="81" s="1" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B81" s="2"/>
+      <c r="C81" s="1">
+        <v>1303</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E81" s="1">
+        <v>1</v>
+      </c>
+      <c r="F81" s="4">
+        <v>0</v>
+      </c>
+      <c r="G81" s="1">
+        <v>2</v>
+      </c>
+      <c r="H81" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="I81" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="J81" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="L81" s="2"/>
+    </row>
+    <row r="82" customHeight="1" spans="2:12">
+      <c r="C82" s="1">
+        <v>1304</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="E82" s="1">
+        <v>1</v>
+      </c>
+      <c r="F82" s="4">
+        <v>0</v>
+      </c>
+      <c r="G82" s="1">
+        <v>2</v>
+      </c>
+      <c r="H82" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="I82" s="8" t="s">
+        <v>485</v>
+      </c>
+      <c r="J82" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="2:12">
+      <c r="C83" s="1">
+        <v>1305</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="E83" s="1">
+        <v>1</v>
+      </c>
+      <c r="F83" s="4">
+        <v>0</v>
+      </c>
+      <c r="G83" s="1">
+        <v>2</v>
+      </c>
+      <c r="H83" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="I83" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="J83" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="2:12">
+      <c r="C84" s="1">
+        <v>1306</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E84" s="1">
+        <v>1</v>
+      </c>
+      <c r="F84" s="4">
+        <v>0</v>
+      </c>
+      <c r="G84" s="1">
+        <v>2</v>
+      </c>
+      <c r="H84" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="I84" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="J84" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K84" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="I77" s="8" t="s">
-        <v>479</v>
-      </c>
-      <c r="J77" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="K77" s="6" t="s">
-        <v>478</v>
-      </c>
+    </row>
+    <row r="85" customHeight="1" spans="2:12">
+      <c r="C85" s="1"/>
+      <c r="D85" s="1"/>
+      <c r="E85" s="1"/>
+      <c r="F85" s="4"/>
+      <c r="G85" s="1"/>
+      <c r="H85" s="1"/>
+      <c r="I85" s="1"/>
+      <c r="J85" s="1"/>
+      <c r="K85" s="1"/>
+    </row>
+    <row r="86" customHeight="1" spans="2:12">
+      <c r="C86" s="2">
+        <v>2041</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="E86" s="1">
+        <v>1</v>
+      </c>
+      <c r="F86" s="4">
+        <v>0</v>
+      </c>
+      <c r="G86" s="1">
+        <v>2</v>
+      </c>
+      <c r="H86" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="I86" s="8" t="s">
+        <v>489</v>
+      </c>
+      <c r="J86" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K86" s="5" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="2:12">
+      <c r="C87" s="2">
+        <v>2042</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="E87" s="1">
+        <v>1</v>
+      </c>
+      <c r="F87" s="4">
+        <v>0</v>
+      </c>
+      <c r="G87" s="1">
+        <v>2</v>
+      </c>
+      <c r="H87" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="I87" s="8" t="s">
+        <v>491</v>
+      </c>
+      <c r="J87" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K87" s="5" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" spans="2:12">
+      <c r="C88" s="2">
+        <v>2043</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="E88" s="1">
+        <v>1</v>
+      </c>
+      <c r="F88" s="4">
+        <v>0</v>
+      </c>
+      <c r="G88" s="1">
+        <v>2</v>
+      </c>
+      <c r="H88" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="I88" s="8" t="s">
+        <v>493</v>
+      </c>
+      <c r="J88" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K88" s="5" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="2:12">
+      <c r="C89" s="2">
+        <v>2044</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>494</v>
+      </c>
+      <c r="E89" s="1">
+        <v>1</v>
+      </c>
+      <c r="F89" s="4">
+        <v>0</v>
+      </c>
+      <c r="G89" s="1">
+        <v>2</v>
+      </c>
+      <c r="H89" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="I89" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="J89" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K89" s="5" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" spans="2:12">
+      <c r="C90" s="2">
+        <v>2045</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="E90" s="1">
+        <v>1</v>
+      </c>
+      <c r="F90" s="4">
+        <v>0</v>
+      </c>
+      <c r="G90" s="1">
+        <v>2</v>
+      </c>
+      <c r="H90" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="I90" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="J90" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K90" s="5" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" spans="2:12">
+      <c r="C91" s="2">
+        <v>2046</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="E91" s="1">
+        <v>1</v>
+      </c>
+      <c r="F91" s="4">
+        <v>0</v>
+      </c>
+      <c r="G91" s="1">
+        <v>2</v>
+      </c>
+      <c r="H91" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="I91" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="J91" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K91" s="5" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" spans="2:12">
+      <c r="C92" s="2">
+        <v>2047</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="E92" s="1">
+        <v>1</v>
+      </c>
+      <c r="F92" s="4">
+        <v>0</v>
+      </c>
+      <c r="G92" s="1">
+        <v>2</v>
+      </c>
+      <c r="H92" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="I92" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="J92" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K92" s="5" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" spans="2:12">
+      <c r="C93" s="2">
+        <v>2048</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="E93" s="1">
+        <v>1</v>
+      </c>
+      <c r="F93" s="4">
+        <v>0</v>
+      </c>
+      <c r="G93" s="1">
+        <v>2</v>
+      </c>
+      <c r="H93" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="I93" s="8" t="s">
+        <v>501</v>
+      </c>
+      <c r="J93" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K93" s="5" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="94" customHeight="1" spans="2:12">
+      <c r="C94" s="2">
+        <v>2049</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="E94" s="1">
+        <v>1</v>
+      </c>
+      <c r="F94" s="4">
+        <v>0</v>
+      </c>
+      <c r="G94" s="1">
+        <v>2</v>
+      </c>
+      <c r="H94" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="I94" s="8" t="s">
+        <v>503</v>
+      </c>
+      <c r="J94" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K94" s="5" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="95" customHeight="1" spans="2:12">
+      <c r="C95" s="2">
+        <v>2050</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="E95" s="1">
+        <v>1</v>
+      </c>
+      <c r="F95" s="4">
+        <v>0</v>
+      </c>
+      <c r="G95" s="1">
+        <v>2</v>
+      </c>
+      <c r="H95" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="I95" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="J95" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K95" s="5" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="96" customHeight="1" spans="2:12">
+      <c r="C96" s="2">
+        <v>2051</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="E96" s="1">
+        <v>1</v>
+      </c>
+      <c r="F96" s="4">
+        <v>0</v>
+      </c>
+      <c r="G96" s="1">
+        <v>2</v>
+      </c>
+      <c r="H96" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="I96" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="J96" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K96" s="5" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="97" customHeight="1" spans="3:11">
+      <c r="I97" s="1"/>
+    </row>
+    <row r="98" customHeight="1" spans="3:11">
+      <c r="C98" s="2">
+        <v>2052</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>508</v>
+      </c>
+      <c r="E98" s="1">
+        <v>1</v>
+      </c>
+      <c r="F98" s="4">
+        <v>0</v>
+      </c>
+      <c r="G98" s="1">
+        <v>2</v>
+      </c>
+      <c r="H98" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="I98" s="8" t="s">
+        <v>509</v>
+      </c>
+      <c r="J98" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K98" s="6" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="99" customHeight="1" spans="3:11">
+      <c r="C99" s="2">
+        <v>2053</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="E99" s="1">
+        <v>1</v>
+      </c>
+      <c r="F99" s="4">
+        <v>0</v>
+      </c>
+      <c r="G99" s="1">
+        <v>2</v>
+      </c>
+      <c r="H99" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="I99" s="8" t="s">
+        <v>511</v>
+      </c>
+      <c r="J99" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K99" s="6" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="100" customHeight="1" spans="3:11">
+      <c r="C100" s="2">
+        <v>2054</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>512</v>
+      </c>
+      <c r="E100" s="1">
+        <v>1</v>
+      </c>
+      <c r="F100" s="4">
+        <v>0</v>
+      </c>
+      <c r="G100" s="1">
+        <v>2</v>
+      </c>
+      <c r="H100" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="I100" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="J100" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K100" s="6" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="101" customHeight="1" spans="3:11">
+      <c r="C101" s="2">
+        <v>2055</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="E101" s="1">
+        <v>1</v>
+      </c>
+      <c r="F101" s="4">
+        <v>0</v>
+      </c>
+      <c r="G101" s="1">
+        <v>2</v>
+      </c>
+      <c r="H101" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="I101" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="J101" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K101" s="6" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="102" customHeight="1" spans="3:11">
+      <c r="C102" s="2">
+        <v>2056</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="E102" s="1">
+        <v>1</v>
+      </c>
+      <c r="F102" s="4">
+        <v>0</v>
+      </c>
+      <c r="G102" s="1">
+        <v>2</v>
+      </c>
+      <c r="H102" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="I102" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="J102" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K102" s="6" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="103" customHeight="1" spans="3:11">
+      <c r="C103" s="2">
+        <v>2057</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="E103" s="1">
+        <v>1</v>
+      </c>
+      <c r="F103" s="4">
+        <v>0</v>
+      </c>
+      <c r="G103" s="1">
+        <v>2</v>
+      </c>
+      <c r="H103" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="I103" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="J103" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K103" s="6" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="104" customHeight="1" spans="3:11">
+      <c r="C104" s="2">
+        <v>2058</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="E104" s="1">
+        <v>1</v>
+      </c>
+      <c r="F104" s="4">
+        <v>0</v>
+      </c>
+      <c r="G104" s="1">
+        <v>2</v>
+      </c>
+      <c r="H104" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="I104" s="8" t="s">
+        <v>519</v>
+      </c>
+      <c r="J104" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K104" s="6" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="105" customHeight="1" spans="3:11">
+      <c r="C105" s="2">
+        <v>2059</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="E105" s="1">
+        <v>1</v>
+      </c>
+      <c r="F105" s="4">
+        <v>0</v>
+      </c>
+      <c r="G105" s="1">
+        <v>2</v>
+      </c>
+      <c r="H105" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="I105" s="8" t="s">
+        <v>521</v>
+      </c>
+      <c r="J105" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K105" s="6" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" spans="3:11">
+      <c r="C106" s="2">
+        <v>2060</v>
+      </c>
+      <c r="D106" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="E106" s="1">
+        <v>1</v>
+      </c>
+      <c r="F106" s="4">
+        <v>0</v>
+      </c>
+      <c r="G106" s="1">
+        <v>2</v>
+      </c>
+      <c r="H106" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="I106" s="8" t="s">
+        <v>523</v>
+      </c>
+      <c r="J106" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K106" s="6" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="107" customHeight="1" spans="3:11">
+      <c r="C107" s="2">
+        <v>2061</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="E107" s="1">
+        <v>1</v>
+      </c>
+      <c r="F107" s="4">
+        <v>0</v>
+      </c>
+      <c r="G107" s="1">
+        <v>2</v>
+      </c>
+      <c r="H107" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="I107" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="J107" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K107" s="6" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="108" customHeight="1" spans="3:11">
+      <c r="C108" s="2">
+        <v>2062</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="E108" s="1">
+        <v>1</v>
+      </c>
+      <c r="F108" s="4">
+        <v>0</v>
+      </c>
+      <c r="G108" s="1">
+        <v>2</v>
+      </c>
+      <c r="H108" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="I108" s="8" t="s">
+        <v>526</v>
+      </c>
+      <c r="J108" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K108" s="6" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="109" customHeight="1" spans="3:11">
+      <c r="D109" s="6"/>
+    </row>
+    <row r="110" customHeight="1" spans="3:11">
+      <c r="C110" s="2">
+        <v>2063</v>
+      </c>
+      <c r="D110" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E110" s="1">
+        <v>1</v>
+      </c>
+      <c r="F110" s="4">
+        <v>0</v>
+      </c>
+      <c r="G110" s="1">
+        <v>2</v>
+      </c>
+      <c r="H110" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="I110" s="8" t="s">
+        <v>528</v>
+      </c>
+      <c r="J110" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K110" s="6" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="111" customHeight="1" spans="3:11">
+      <c r="C111" s="2">
+        <v>2064</v>
+      </c>
+      <c r="D111" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="E111" s="1">
+        <v>1</v>
+      </c>
+      <c r="F111" s="4">
+        <v>0</v>
+      </c>
+      <c r="G111" s="1">
+        <v>2</v>
+      </c>
+      <c r="H111" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="I111" s="8" t="s">
+        <v>530</v>
+      </c>
+      <c r="J111" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K111" s="6" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="112" customHeight="1" spans="3:11">
+      <c r="C112" s="2">
+        <v>2065</v>
+      </c>
+      <c r="D112" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="E112" s="1">
+        <v>1</v>
+      </c>
+      <c r="F112" s="4">
+        <v>0</v>
+      </c>
+      <c r="G112" s="1">
+        <v>2</v>
+      </c>
+      <c r="H112" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="I112" s="8" t="s">
+        <v>532</v>
+      </c>
+      <c r="J112" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K112" s="6" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="113" customHeight="1" spans="3:11">
+      <c r="C113" s="2">
+        <v>2066</v>
+      </c>
+      <c r="D113" s="6" t="s">
+        <v>533</v>
+      </c>
+      <c r="E113" s="1">
+        <v>1</v>
+      </c>
+      <c r="F113" s="4">
+        <v>0</v>
+      </c>
+      <c r="G113" s="1">
+        <v>2</v>
+      </c>
+      <c r="H113" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="I113" s="8" t="s">
+        <v>534</v>
+      </c>
+      <c r="J113" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K113" s="6" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="114" customHeight="1" spans="3:11">
+      <c r="C114" s="2">
+        <v>2067</v>
+      </c>
+      <c r="D114" s="6" t="s">
+        <v>535</v>
+      </c>
+      <c r="E114" s="1">
+        <v>1</v>
+      </c>
+      <c r="F114" s="4">
+        <v>0</v>
+      </c>
+      <c r="G114" s="1">
+        <v>2</v>
+      </c>
+      <c r="H114" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="I114" s="8" t="s">
+        <v>536</v>
+      </c>
+      <c r="J114" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K114" s="6" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="115" customHeight="1" spans="3:11">
+      <c r="C115" s="2">
+        <v>2068</v>
+      </c>
+      <c r="D115" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="E115" s="1">
+        <v>1</v>
+      </c>
+      <c r="F115" s="4">
+        <v>0</v>
+      </c>
+      <c r="G115" s="1">
+        <v>2</v>
+      </c>
+      <c r="H115" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="I115" s="8" t="s">
+        <v>537</v>
+      </c>
+      <c r="J115" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K115" s="6" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="116" customHeight="1" spans="3:11">
+      <c r="C116" s="2">
+        <v>2069</v>
+      </c>
+      <c r="D116" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="E116" s="1">
+        <v>1</v>
+      </c>
+      <c r="F116" s="4">
+        <v>0</v>
+      </c>
+      <c r="G116" s="1">
+        <v>2</v>
+      </c>
+      <c r="H116" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="I116" s="8" t="s">
+        <v>539</v>
+      </c>
+      <c r="J116" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K116" s="6" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="117" customHeight="1" spans="3:11">
+      <c r="C117" s="2">
+        <v>2070</v>
+      </c>
+      <c r="D117" s="6" t="s">
+        <v>540</v>
+      </c>
+      <c r="E117" s="1">
+        <v>1</v>
+      </c>
+      <c r="F117" s="4">
+        <v>0</v>
+      </c>
+      <c r="G117" s="1">
+        <v>2</v>
+      </c>
+      <c r="H117" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="I117" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="J117" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K117" s="6" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="118" customHeight="1" spans="3:11">
+      <c r="C118" s="2">
+        <v>2071</v>
+      </c>
+      <c r="D118" s="6" t="s">
+        <v>542</v>
+      </c>
+      <c r="E118" s="1">
+        <v>1</v>
+      </c>
+      <c r="F118" s="4">
+        <v>0</v>
+      </c>
+      <c r="G118" s="1">
+        <v>2</v>
+      </c>
+      <c r="H118" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="I118" s="8" t="s">
+        <v>543</v>
+      </c>
+      <c r="J118" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K118" s="6" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="119" customHeight="1" spans="3:11">
+      <c r="C119" s="2">
+        <v>2072</v>
+      </c>
+      <c r="D119" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="E119" s="1">
+        <v>1</v>
+      </c>
+      <c r="F119" s="4">
+        <v>0</v>
+      </c>
+      <c r="G119" s="1">
+        <v>2</v>
+      </c>
+      <c r="H119" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="I119" s="8" t="s">
+        <v>544</v>
+      </c>
+      <c r="J119" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K119" s="6" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="120" customHeight="1" spans="3:11">
+      <c r="D120" s="6"/>
+    </row>
+    <row r="122" customHeight="1" spans="3:11">
+      <c r="D122" s="6"/>
+    </row>
+    <row r="123" customHeight="1" spans="3:11">
+      <c r="D123" s="6"/>
+    </row>
+    <row r="124" customHeight="1" spans="3:11">
+      <c r="D124" s="6"/>
+    </row>
+    <row r="125" customHeight="1" spans="3:11">
+      <c r="D125" s="6"/>
+    </row>
+    <row r="126" customHeight="1" spans="3:11">
+      <c r="D126" s="6"/>
+    </row>
+    <row r="128" customHeight="1" spans="3:11">
+      <c r="D128" s="6"/>
+    </row>
+    <row r="129" customHeight="1" spans="4:4">
+      <c r="D129" s="6"/>
+    </row>
+    <row r="130" customHeight="1" spans="4:4">
+      <c r="D130" s="6"/>
+    </row>
+    <row r="131" customHeight="1" spans="4:4">
+      <c r="D131" s="6"/>
+    </row>
+    <row r="132" customHeight="1" spans="4:4">
+      <c r="D132" s="6"/>
+    </row>
+    <row r="134" customHeight="1" spans="4:4">
+      <c r="D134" s="6"/>
+    </row>
+    <row r="135" customHeight="1" spans="4:4">
+      <c r="D135" s="6"/>
+    </row>
+    <row r="136" customHeight="1" spans="4:4">
+      <c r="D136" s="6"/>
+    </row>
+    <row r="137" customHeight="1" spans="4:4">
+      <c r="D137" s="6"/>
+    </row>
+    <row r="138" customHeight="1" spans="4:4">
+      <c r="D138" s="6"/>
+    </row>
+    <row r="140" customHeight="1" spans="4:4">
+      <c r="D140" s="6"/>
+    </row>
+    <row r="141" customHeight="1" spans="4:4">
+      <c r="D141" s="6"/>
+    </row>
+    <row r="142" customHeight="1" spans="4:4">
+      <c r="D142" s="6"/>
+    </row>
+    <row r="143" customHeight="1" spans="4:4">
+      <c r="D143" s="6"/>
+    </row>
+    <row r="144" customHeight="1" spans="4:4">
+      <c r="D144" s="6"/>
+    </row>
+    <row r="146" customHeight="1" spans="4:4">
+      <c r="D146" s="6"/>
+    </row>
+    <row r="147" customHeight="1" spans="4:4">
+      <c r="D147" s="6"/>
+    </row>
+    <row r="148" customHeight="1" spans="4:4">
+      <c r="D148" s="6"/>
+    </row>
+    <row r="149" customHeight="1" spans="4:4">
+      <c r="D149" s="6"/>
+    </row>
+    <row r="150" customHeight="1" spans="4:4">
+      <c r="D150" s="6"/>
+    </row>
+    <row r="152" customHeight="1" spans="4:4">
+      <c r="D152" s="6"/>
+    </row>
+    <row r="153" customHeight="1" spans="4:4">
+      <c r="D153" s="6"/>
+    </row>
+    <row r="154" customHeight="1" spans="4:4">
+      <c r="D154" s="6"/>
+    </row>
+    <row r="155" customHeight="1" spans="4:4">
+      <c r="D155" s="6"/>
+    </row>
+    <row r="156" customHeight="1" spans="4:4">
+      <c r="D156" s="6"/>
+    </row>
+    <row r="158" customHeight="1" spans="4:4">
+      <c r="D158" s="6"/>
+    </row>
+    <row r="159" customHeight="1" spans="4:4">
+      <c r="D159" s="6"/>
+    </row>
+    <row r="160" customHeight="1" spans="4:4">
+      <c r="D160" s="6"/>
+    </row>
+    <row r="161" customHeight="1" spans="4:4">
+      <c r="D161" s="6"/>
+    </row>
+    <row r="162" customHeight="1" spans="4:4">
+      <c r="D162" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -1618,112 +1618,112 @@
     <t>落雷术·入圣</t>
   </si>
   <si>
-    <t>4001,4002,4003,4004,4005,4006</t>
+    <t>3101,3102,3103,3104,3105,3106</t>
   </si>
   <si>
     <t>落雷术·命中</t>
   </si>
   <si>
-    <t>4007,4008,4009,4010,4011,4012</t>
+    <t>3107,3108,3109,3110,3111,3112</t>
   </si>
   <si>
     <t>法力盾·入圣</t>
   </si>
   <si>
-    <t>4013,4014,4015,4016,4017,4018</t>
+    <t>3113,3114,3115,3116,3117,3118</t>
   </si>
   <si>
     <t>法术精通·入圣</t>
   </si>
   <si>
-    <t>4019,4020,4021,4022,4023,4024</t>
-  </si>
-  <si>
-    <t>4025,4026,4027,4028,4029,4030</t>
+    <t>3119,3120,3121,3122,3123,3124</t>
+  </si>
+  <si>
+    <t>3125,3126,3127,3128,3129,3130</t>
   </si>
   <si>
     <t>心灵传送·入圣</t>
   </si>
   <si>
-    <t>4031,4032,4033,4034,4035,4036</t>
-  </si>
-  <si>
-    <t>4037,4038,4039,4040,4041,4042</t>
+    <t>3131,3132,3133,3134,3135,3136</t>
+  </si>
+  <si>
+    <t>3137,3138,3139,3140,3141,3142</t>
   </si>
   <si>
     <t>分身术·入圣</t>
   </si>
   <si>
-    <t>4043,4044,4045,4046,4047,4048</t>
+    <t>3143,3144,3145,3146,3147,3148</t>
   </si>
   <si>
     <t>法师之魂·入圣</t>
   </si>
   <si>
-    <t>4049,4050,4051,4052,4053,4054</t>
+    <t>3149,3150,3151,3152,3153,3154</t>
   </si>
   <si>
     <t>魔尊附体·入圣</t>
   </si>
   <si>
-    <t>4055,4056,4057,4058,4059,4060</t>
-  </si>
-  <si>
-    <t>4061,4062,4063,4064,4065,4066</t>
+    <t>3155,3156,3157,3158,3159,3160</t>
+  </si>
+  <si>
+    <t>3161,3162,3163,3164,3165,3166</t>
   </si>
   <si>
     <t>驱魔符·入圣</t>
   </si>
   <si>
-    <t>5001,5002,5003,5004,5005,5006</t>
+    <t>3201,3202,3203,3204,3205,3206</t>
   </si>
   <si>
     <t>驱魔符·命中</t>
   </si>
   <si>
-    <t>5007,5008,5009,5010,5011,5012</t>
+    <t>3207,3208,3209,3210,3211,3212</t>
   </si>
   <si>
     <t>道力盾·入圣</t>
   </si>
   <si>
-    <t>5013,5014,5015,5016,5017,5018</t>
+    <t>3213,3214,3215,3216,3217,3218</t>
   </si>
   <si>
     <t>道力精通·入圣</t>
   </si>
   <si>
-    <t>5019,5020,5021,5022,5023,5024</t>
+    <t>3219,3220,3221,3222,3223,3224</t>
   </si>
   <si>
     <t>隐身道法·入圣</t>
   </si>
   <si>
-    <t>5025,5026,5027,5028,5029,5030</t>
-  </si>
-  <si>
-    <t>5031,5032,5033,5034,5035,5036</t>
+    <t>3225,3226,3227,3228,3229,3230</t>
+  </si>
+  <si>
+    <t>3231,3232,3233,3234,3235,3236</t>
   </si>
   <si>
     <t>无极道体·入圣</t>
   </si>
   <si>
-    <t>5037,5038,5039,5040,5041,5042</t>
+    <t>3237,3238,3239,3240,3241,3242</t>
   </si>
   <si>
     <t>道士之魂·入圣</t>
   </si>
   <si>
-    <t>5043,5044,5045,5046,5047,5048</t>
+    <t>3243,3244,3245,3246,3247,3248</t>
   </si>
   <si>
     <t>召唤白虎·入圣</t>
   </si>
   <si>
-    <t>5049,5050,5051,5052,5053,5054</t>
-  </si>
-  <si>
-    <t>5055,5056,5057,5058,5059,5060</t>
+    <t>3249,3250,3251,3252,3253,3254</t>
+  </si>
+  <si>
+    <t>3255,3256,3257,3258,3259,3260</t>
   </si>
 </sst>
 </file>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -8344,13 +8344,13 @@
         <v>2</v>
       </c>
       <c r="H79" s="8" t="s">
-        <v>133</v>
+        <v>167</v>
       </c>
       <c r="I79" s="8" t="s">
         <v>482</v>
       </c>
       <c r="J79" s="8" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="K79" s="1" t="s">
         <v>392</v>
@@ -8374,13 +8374,13 @@
         <v>2</v>
       </c>
       <c r="H80" s="8" t="s">
-        <v>394</v>
+        <v>133</v>
       </c>
       <c r="I80" s="8" t="s">
         <v>483</v>
       </c>
       <c r="J80" s="8" t="s">
-        <v>396</v>
+        <v>40</v>
       </c>
       <c r="K80" s="1" t="s">
         <v>397</v>
@@ -8405,7 +8405,7 @@
         <v>2</v>
       </c>
       <c r="H81" s="8" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="I81" s="8" t="s">
         <v>484</v>
@@ -8435,13 +8435,13 @@
         <v>2</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>133</v>
+        <v>185</v>
       </c>
       <c r="I82" s="8" t="s">
         <v>485</v>
       </c>
       <c r="J82" s="8" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="K82" s="1" t="s">
         <v>404</v>
@@ -8470,7 +8470,7 @@
         <v>486</v>
       </c>
       <c r="J83" s="8" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="K83" s="1" t="s">
         <v>407</v>
@@ -8499,7 +8499,7 @@
         <v>487</v>
       </c>
       <c r="J84" s="8" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="K84" s="1" t="s">
         <v>410</v>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1179" uniqueCount="550">
   <si>
     <t>_id</t>
   </si>
@@ -562,7 +562,10 @@
     <t>极神器自选</t>
   </si>
   <si>
-    <t>47</t>
+    <t>47,48,49,50</t>
+  </si>
+  <si>
+    <t>全极神器自选</t>
   </si>
   <si>
     <t>道戒自选</t>
@@ -1040,6 +1043,18 @@
   </si>
   <si>
     <t>914,915,916</t>
+  </si>
+  <si>
+    <t>80粉色坐骑自选</t>
+  </si>
+  <si>
+    <t>921,922,923</t>
+  </si>
+  <si>
+    <t>100粉色坐骑自选</t>
+  </si>
+  <si>
+    <t>924,925,926</t>
   </si>
   <si>
     <t>金色刺杀自选</t>
@@ -4303,7 +4318,7 @@
         <v>91</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>132</v>
+        <v>158</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1" spans="1:11">
@@ -4311,7 +4326,7 @@
         <v>53</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E57" s="1">
         <v>1</v>
@@ -4326,13 +4341,13 @@
         <v>77</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J57" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="58" customFormat="1" customHeight="1" spans="1:11">
@@ -4340,7 +4355,7 @@
         <v>54</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E58" s="1">
         <v>0</v>
@@ -4352,16 +4367,16 @@
         <v>1</v>
       </c>
       <c r="H58" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="I58" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="J58" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="K58" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="I58" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="J58" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="59" customFormat="1" customHeight="1" spans="1:11">
@@ -4371,7 +4386,7 @@
         <v>55</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E59" s="1">
         <v>1</v>
@@ -4386,13 +4401,13 @@
         <v>139</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J59" s="8" t="s">
         <v>141</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="60" customFormat="1" customHeight="1" spans="1:11">
@@ -4415,7 +4430,7 @@
         <v>88</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E61" s="1">
         <v>1</v>
@@ -4427,16 +4442,16 @@
         <v>2</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J61" s="8" t="s">
         <v>141</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="62" customFormat="1" customHeight="1" spans="1:11">
@@ -4446,7 +4461,7 @@
         <v>89</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E62" s="1">
         <v>1</v>
@@ -4458,16 +4473,16 @@
         <v>2</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I62" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J62" s="8" t="s">
         <v>141</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="63" customFormat="1" customHeight="1" spans="1:11">
@@ -4477,7 +4492,7 @@
         <v>90</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E63" s="1">
         <v>1</v>
@@ -4489,16 +4504,16 @@
         <v>2</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J63" s="8" t="s">
         <v>141</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="64" customFormat="1" customHeight="1" spans="1:11">
@@ -4508,7 +4523,7 @@
         <v>91</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E64" s="1">
         <v>1</v>
@@ -4523,13 +4538,13 @@
         <v>133</v>
       </c>
       <c r="I64" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J64" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="65" customFormat="1" customHeight="1" spans="1:11">
@@ -4539,7 +4554,7 @@
         <v>94</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E65" s="1">
         <v>1</v>
@@ -4551,16 +4566,16 @@
         <v>2</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J65" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="66" customFormat="1" customHeight="1" spans="1:11">
@@ -4570,7 +4585,7 @@
         <v>95</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E66" s="1">
         <v>1</v>
@@ -4582,16 +4597,16 @@
         <v>2</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I66" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J66" s="8" t="s">
         <v>91</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="67" customFormat="1" customHeight="1" spans="1:11">
@@ -4599,7 +4614,7 @@
         <v>96</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E67" s="1">
         <v>0</v>
@@ -4611,16 +4626,16 @@
         <v>2</v>
       </c>
       <c r="H67" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="I67" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="J67" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="K67" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="I67" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="J67" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="68" customFormat="1" customHeight="1" spans="1:11">
@@ -4628,7 +4643,7 @@
         <v>97</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E68" s="1">
         <v>1</v>
@@ -4640,16 +4655,16 @@
         <v>2</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I68" s="8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J68" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="69" customFormat="1" customHeight="1" spans="1:11">
@@ -4657,7 +4672,7 @@
         <v>98</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E69" s="1">
         <v>1</v>
@@ -4669,16 +4684,16 @@
         <v>2</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J69" s="8" t="s">
         <v>91</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="70" customFormat="1" customHeight="1" spans="1:11">
@@ -4686,7 +4701,7 @@
         <v>99</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E70" s="1">
         <v>0</v>
@@ -4698,16 +4713,16 @@
         <v>2</v>
       </c>
       <c r="H70" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="I70" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="J70" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="K70" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="I70" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="J70" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="K70" s="1" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="71" customFormat="1" customHeight="1" spans="1:11">
@@ -4715,7 +4730,7 @@
         <v>100</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E71" s="1">
         <v>0</v>
@@ -4727,16 +4742,16 @@
         <v>2</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I71" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="J71" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="K71" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="J71" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="K71" s="1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="72" customFormat="1" customHeight="1" spans="1:11">
@@ -4744,7 +4759,7 @@
         <v>101</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E72" s="1">
         <v>0</v>
@@ -4756,16 +4771,16 @@
         <v>2</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I72" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="J72" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="K72" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="J72" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="K72" s="1" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="73" customFormat="1" customHeight="1" spans="1:11">
@@ -4773,7 +4788,7 @@
         <v>102</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E73" s="1">
         <v>0</v>
@@ -4785,16 +4800,16 @@
         <v>2</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I73" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="J73" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="K73" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="J73" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="K73" s="1" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="74" customFormat="1" customHeight="1" spans="1:11">
@@ -4802,7 +4817,7 @@
         <v>103</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E74" s="1">
         <v>0</v>
@@ -4814,16 +4829,16 @@
         <v>2</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I74" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="J74" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="K74" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="J74" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="K74" s="1" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="75" customFormat="1" customHeight="1" spans="1:11">
@@ -4831,7 +4846,7 @@
         <v>104</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E75" s="1">
         <v>0</v>
@@ -4843,16 +4858,16 @@
         <v>2</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I75" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="J75" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="K75" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="J75" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="K75" s="1" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="76" customFormat="1" customHeight="1" spans="1:11">
@@ -4860,7 +4875,7 @@
         <v>105</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E76" s="1">
         <v>0</v>
@@ -4872,16 +4887,16 @@
         <v>2</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I76" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="J76" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="K76" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="J76" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="K76" s="1" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="77" ht="14"/>
@@ -4890,7 +4905,7 @@
         <v>106</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E78" s="1">
         <v>1</v>
@@ -4902,16 +4917,16 @@
         <v>1</v>
       </c>
       <c r="H78" s="8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I78" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J78" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="79" customFormat="1" customHeight="1" spans="1:11">
@@ -4919,7 +4934,7 @@
         <v>107</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E79" s="1">
         <v>1</v>
@@ -4934,7 +4949,7 @@
         <v>64</v>
       </c>
       <c r="I79" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J79" s="8" t="s">
         <v>40</v>
@@ -4948,7 +4963,7 @@
         <v>108</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E80" s="1">
         <v>1</v>
@@ -4963,13 +4978,13 @@
         <v>64</v>
       </c>
       <c r="I80" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="J80" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="81" ht="14"/>
@@ -4978,7 +4993,7 @@
         <v>109</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E82" s="1">
         <v>1</v>
@@ -4990,16 +5005,16 @@
         <v>2</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I82" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J82" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="83" customFormat="1" customHeight="1" spans="1:11">
@@ -5007,7 +5022,7 @@
         <v>110</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E83" s="1">
         <v>1</v>
@@ -5019,16 +5034,16 @@
         <v>2</v>
       </c>
       <c r="H83" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I83" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J83" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="84" customFormat="1" customHeight="1" spans="1:11">
@@ -5036,7 +5051,7 @@
         <v>111</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E84" s="1">
         <v>1</v>
@@ -5048,16 +5063,16 @@
         <v>2</v>
       </c>
       <c r="H84" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I84" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J84" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="85" customFormat="1" customHeight="1" spans="1:11">
@@ -5065,7 +5080,7 @@
         <v>112</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E85" s="1">
         <v>1</v>
@@ -5077,16 +5092,16 @@
         <v>2</v>
       </c>
       <c r="H85" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I85" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="J85" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="86" customFormat="1" customHeight="1" spans="1:11">
@@ -5094,7 +5109,7 @@
         <v>113</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E86" s="1">
         <v>1</v>
@@ -5106,16 +5121,16 @@
         <v>2</v>
       </c>
       <c r="H86" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I86" s="8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J86" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="87" customFormat="1" customHeight="1" spans="1:11">
@@ -5123,7 +5138,7 @@
         <v>114</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E87" s="1">
         <v>1</v>
@@ -5135,16 +5150,16 @@
         <v>2</v>
       </c>
       <c r="H87" s="8" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I87" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J87" s="8" t="s">
         <v>91</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="88" customFormat="1" customHeight="1" spans="1:11">
@@ -5152,7 +5167,7 @@
         <v>115</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E88" s="1">
         <v>1</v>
@@ -5164,31 +5179,31 @@
         <v>2</v>
       </c>
       <c r="H88" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I88" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J88" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="89" ht="14"/>
     <row r="90" customFormat="1" customHeight="1" spans="1:11">
       <c r="A90" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C90" s="1">
         <v>118</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E90" s="1">
         <v>1</v>
@@ -5200,30 +5215,30 @@
         <v>2</v>
       </c>
       <c r="H90" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I90" s="8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J90" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K90" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="91" customFormat="1" customHeight="1" spans="1:11">
       <c r="A91" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C91" s="1">
         <v>119</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E91" s="1">
         <v>1</v>
@@ -5235,30 +5250,30 @@
         <v>2</v>
       </c>
       <c r="H91" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I91" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J91" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K91" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="92" customFormat="1" customHeight="1" spans="1:11">
       <c r="A92" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C92" s="1">
         <v>120</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E92" s="1">
         <v>1</v>
@@ -5270,30 +5285,30 @@
         <v>2</v>
       </c>
       <c r="H92" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I92" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J92" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K92" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="93" customFormat="1" customHeight="1" spans="1:11">
       <c r="A93" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C93" s="1">
         <v>121</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E93" s="1">
         <v>1</v>
@@ -5305,30 +5320,30 @@
         <v>2</v>
       </c>
       <c r="H93" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I93" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J93" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K93" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="94" customFormat="1" customHeight="1" spans="1:11">
       <c r="A94" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C94" s="1">
         <v>122</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E94" s="1">
         <v>1</v>
@@ -5340,30 +5355,30 @@
         <v>2</v>
       </c>
       <c r="H94" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I94" s="8" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J94" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="95" customFormat="1" customHeight="1" spans="1:11">
       <c r="A95" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C95" s="1">
         <v>123</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E95" s="1">
         <v>1</v>
@@ -5375,30 +5390,30 @@
         <v>2</v>
       </c>
       <c r="H95" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I95" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J95" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K95" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="96" customFormat="1" customHeight="1" spans="1:11">
       <c r="A96" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C96" s="1">
         <v>124</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E96" s="1">
         <v>1</v>
@@ -5410,30 +5425,30 @@
         <v>2</v>
       </c>
       <c r="H96" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I96" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J96" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="97" customFormat="1" customHeight="1" spans="1:11">
       <c r="A97" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C97" s="1">
         <v>125</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E97" s="1">
         <v>1</v>
@@ -5445,30 +5460,30 @@
         <v>2</v>
       </c>
       <c r="H97" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I97" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J97" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="98" customFormat="1" customHeight="1" spans="1:11">
       <c r="A98" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C98" s="1">
         <v>126</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E98" s="1">
         <v>1</v>
@@ -5480,30 +5495,30 @@
         <v>2</v>
       </c>
       <c r="H98" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I98" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J98" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="99" customFormat="1" customHeight="1" spans="1:11">
       <c r="A99" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C99" s="1">
         <v>127</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E99" s="1">
         <v>1</v>
@@ -5515,30 +5530,30 @@
         <v>2</v>
       </c>
       <c r="H99" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I99" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J99" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="100" customFormat="1" customHeight="1" spans="1:11">
       <c r="A100" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C100" s="1">
         <v>128</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E100" s="1">
         <v>1</v>
@@ -5550,30 +5565,30 @@
         <v>2</v>
       </c>
       <c r="H100" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I100" s="8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J100" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="101" customFormat="1" customHeight="1" spans="1:11">
       <c r="A101" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C101" s="1">
         <v>129</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E101" s="1">
         <v>1</v>
@@ -5585,30 +5600,30 @@
         <v>2</v>
       </c>
       <c r="H101" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I101" s="8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J101" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="102" customFormat="1" customHeight="1" spans="1:11">
       <c r="A102" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C102" s="1">
         <v>130</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E102" s="1">
         <v>1</v>
@@ -5620,30 +5635,30 @@
         <v>2</v>
       </c>
       <c r="H102" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I102" s="8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J102" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="103" customFormat="1" customHeight="1" spans="1:11">
       <c r="A103" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C103" s="1">
         <v>131</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E103" s="1">
         <v>1</v>
@@ -5655,31 +5670,31 @@
         <v>2</v>
       </c>
       <c r="H103" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I103" s="8" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="J103" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="104" ht="14"/>
     <row r="105" customFormat="1" customHeight="1" spans="1:11">
       <c r="A105" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C105" s="1">
         <v>137</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E105" s="1">
         <v>1</v>
@@ -5691,30 +5706,30 @@
         <v>2</v>
       </c>
       <c r="H105" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I105" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J105" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="106" customFormat="1" customHeight="1" spans="1:11">
       <c r="A106" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C106" s="1">
         <v>138</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E106" s="1">
         <v>1</v>
@@ -5726,51 +5741,51 @@
         <v>2</v>
       </c>
       <c r="H106" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="I106" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="J106" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="K106" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="I106" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="J106" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="K106" s="1" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="107" customFormat="1" customHeight="1" spans="1:11">
       <c r="A107" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C107" s="1">
         <v>139</v>
       </c>
       <c r="D107" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E107" s="1">
+        <v>1</v>
+      </c>
+      <c r="F107" s="4">
+        <v>0</v>
+      </c>
+      <c r="G107" s="4">
+        <v>2</v>
+      </c>
+      <c r="H107" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="I107" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="J107" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="E107" s="1">
-        <v>1</v>
-      </c>
-      <c r="F107" s="4">
-        <v>0</v>
-      </c>
-      <c r="G107" s="4">
-        <v>2</v>
-      </c>
-      <c r="H107" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="I107" s="8" t="s">
+      <c r="K107" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="J107" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="K107" s="1" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="108" ht="14"/>
@@ -5787,7 +5802,7 @@
         <v>201</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E117" s="1">
         <v>1</v>
@@ -5799,16 +5814,16 @@
         <v>2</v>
       </c>
       <c r="H117" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I117" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J117" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="118" customFormat="1" customHeight="1" spans="3:11">
@@ -5816,7 +5831,7 @@
         <v>202</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E118" s="1">
         <v>1</v>
@@ -5828,16 +5843,16 @@
         <v>2</v>
       </c>
       <c r="H118" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I118" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J118" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="119" customFormat="1" customHeight="1" spans="3:11">
@@ -5845,7 +5860,7 @@
         <v>203</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E119" s="1">
         <v>1</v>
@@ -5857,16 +5872,16 @@
         <v>2</v>
       </c>
       <c r="H119" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I119" s="8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J119" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="120" customFormat="1" customHeight="1" spans="3:11">
@@ -5874,7 +5889,7 @@
         <v>204</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E120" s="1">
         <v>1</v>
@@ -5886,16 +5901,16 @@
         <v>2</v>
       </c>
       <c r="H120" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I120" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J120" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="121" customFormat="1" customHeight="1" spans="3:11">
@@ -5903,7 +5918,7 @@
         <v>205</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E121" s="1">
         <v>1</v>
@@ -5915,16 +5930,16 @@
         <v>2</v>
       </c>
       <c r="H121" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I121" s="8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J121" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K121" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="122" ht="14"/>
@@ -5933,7 +5948,7 @@
         <v>207</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E123" s="1">
         <v>1</v>
@@ -5945,16 +5960,16 @@
         <v>2</v>
       </c>
       <c r="H123" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I123" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J123" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K123" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="124" customFormat="1" customHeight="1" spans="3:11">
@@ -5962,7 +5977,7 @@
         <v>208</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E124" s="1">
         <v>1</v>
@@ -5974,16 +5989,16 @@
         <v>2</v>
       </c>
       <c r="H124" s="8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="I124" s="8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="J124" s="8" t="s">
         <v>141</v>
       </c>
       <c r="K124" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="125" customFormat="1" customHeight="1" spans="3:11">
@@ -5991,7 +6006,7 @@
         <v>209</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E125" s="1">
         <v>1</v>
@@ -6003,16 +6018,16 @@
         <v>2</v>
       </c>
       <c r="H125" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I125" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J125" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="126" customFormat="1" customHeight="1" spans="3:11">
@@ -6020,28 +6035,28 @@
         <v>210</v>
       </c>
       <c r="D126" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="E126" s="1">
+        <v>1</v>
+      </c>
+      <c r="F126" s="4">
+        <v>0</v>
+      </c>
+      <c r="G126" s="4">
+        <v>2</v>
+      </c>
+      <c r="H126" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="I126" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="J126" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="K126" s="1" t="s">
         <v>302</v>
-      </c>
-      <c r="E126" s="1">
-        <v>1</v>
-      </c>
-      <c r="F126" s="4">
-        <v>0</v>
-      </c>
-      <c r="G126" s="4">
-        <v>2</v>
-      </c>
-      <c r="H126" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="I126" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="J126" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="K126" s="1" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="127" customFormat="1" customHeight="1" spans="3:11">
@@ -6049,7 +6064,7 @@
         <v>211</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E127" s="1">
         <v>1</v>
@@ -6061,16 +6076,16 @@
         <v>2</v>
       </c>
       <c r="H127" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I127" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="J127" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="K127" s="1" t="s">
         <v>306</v>
-      </c>
-      <c r="J127" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="K127" s="1" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="128" customFormat="1" customHeight="1" spans="3:11">
@@ -6078,7 +6093,7 @@
         <v>212</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E128" s="1">
         <v>1</v>
@@ -6090,16 +6105,16 @@
         <v>2</v>
       </c>
       <c r="H128" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I128" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="J128" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="K128" s="1" t="s">
         <v>308</v>
-      </c>
-      <c r="J128" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="K128" s="1" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="129" ht="14"/>
@@ -6109,7 +6124,7 @@
         <v>301</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E131" s="1">
         <v>1</v>
@@ -6121,16 +6136,16 @@
         <v>2</v>
       </c>
       <c r="H131" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="I131" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="J131" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="K131" s="1" t="s">
         <v>310</v>
-      </c>
-      <c r="I131" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="J131" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="K131" s="1" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="132" ht="14" spans="3:11">
@@ -6138,7 +6153,7 @@
         <v>302</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E132" s="1"/>
       <c r="F132" s="4"/>
@@ -6148,12 +6163,12 @@
       <c r="J132" s="1"/>
       <c r="K132" s="1"/>
     </row>
-    <row r="133" ht="14" spans="3:11">
+    <row r="133" spans="3:11">
       <c r="C133" s="1">
         <v>303</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E133" s="1">
         <v>1</v>
@@ -6165,16 +6180,16 @@
         <v>2</v>
       </c>
       <c r="H133" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I133" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="J133" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="K133" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="J133" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="K133" s="1" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="134" customFormat="1" ht="14" spans="3:11">
@@ -6182,7 +6197,7 @@
         <v>304</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E134" s="1">
         <v>1</v>
@@ -6194,20 +6209,76 @@
         <v>2</v>
       </c>
       <c r="H134" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I134" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="J134" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="K134" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="J134" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="K134" s="1" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="135" ht="14"/>
-    <row r="136" ht="14"/>
+    </row>
+    <row r="135" ht="14" spans="3:11">
+      <c r="C135" s="1">
+        <v>305</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E135" s="1">
+        <v>1</v>
+      </c>
+      <c r="F135" s="4">
+        <v>0</v>
+      </c>
+      <c r="G135" s="4">
+        <v>2</v>
+      </c>
+      <c r="H135" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="I135" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="J135" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="K135" s="1" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="136" ht="14" spans="3:11">
+      <c r="C136" s="1">
+        <v>306</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="E136" s="1">
+        <v>1</v>
+      </c>
+      <c r="F136" s="4">
+        <v>0</v>
+      </c>
+      <c r="G136" s="4">
+        <v>2</v>
+      </c>
+      <c r="H136" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="I136" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="J136" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="K136" s="1" t="s">
+        <v>320</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5 H3:K5" errorStyle="warning">
@@ -6333,7 +6404,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -6348,13 +6419,13 @@
         <v>14</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="J6" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6362,7 +6433,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -6377,13 +6448,13 @@
         <v>14</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="J7" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6391,7 +6462,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -6406,13 +6477,13 @@
         <v>14</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="J8" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6420,7 +6491,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -6435,13 +6506,13 @@
         <v>14</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="J9" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6449,7 +6520,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -6464,13 +6535,13 @@
         <v>14</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6478,7 +6549,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -6493,13 +6564,13 @@
         <v>14</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="J11" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6507,7 +6578,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -6522,13 +6593,13 @@
         <v>14</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6536,7 +6607,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -6551,13 +6622,13 @@
         <v>14</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="J13" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6565,7 +6636,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -6580,13 +6651,13 @@
         <v>14</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="J14" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6594,7 +6665,7 @@
         <v>1010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -6609,13 +6680,13 @@
         <v>14</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6623,7 +6694,7 @@
         <v>1011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -6638,13 +6709,13 @@
         <v>14</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="J16" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6652,7 +6723,7 @@
         <v>1012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -6667,13 +6738,13 @@
         <v>14</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="J17" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6681,7 +6752,7 @@
         <v>1013</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -6696,13 +6767,13 @@
         <v>14</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="J18" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6710,7 +6781,7 @@
         <v>1014</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
@@ -6725,13 +6796,13 @@
         <v>14</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="J19" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1"/>
@@ -6740,7 +6811,7 @@
         <v>1101</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -6755,13 +6826,13 @@
         <v>14</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="J21" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6769,7 +6840,7 @@
         <v>1102</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -6784,13 +6855,13 @@
         <v>14</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="J22" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6798,7 +6869,7 @@
         <v>1103</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -6813,13 +6884,13 @@
         <v>14</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="J23" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6827,7 +6898,7 @@
         <v>1104</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -6842,13 +6913,13 @@
         <v>14</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="J24" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6856,7 +6927,7 @@
         <v>1105</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -6871,13 +6942,13 @@
         <v>14</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="J25" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6885,7 +6956,7 @@
         <v>1106</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -6900,13 +6971,13 @@
         <v>14</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="J26" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6914,7 +6985,7 @@
         <v>1107</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -6929,13 +7000,13 @@
         <v>14</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="J27" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6943,7 +7014,7 @@
         <v>1108</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
@@ -6958,13 +7029,13 @@
         <v>14</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="J28" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6972,7 +7043,7 @@
         <v>1109</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -6987,13 +7058,13 @@
         <v>14</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="J29" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -7001,7 +7072,7 @@
         <v>1110</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -7016,13 +7087,13 @@
         <v>14</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="J30" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -7030,7 +7101,7 @@
         <v>1111</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -7045,13 +7116,13 @@
         <v>14</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="J31" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -7059,7 +7130,7 @@
         <v>1112</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -7074,13 +7145,13 @@
         <v>14</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="J32" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="2:12">
@@ -7101,7 +7172,7 @@
         <v>1201</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
@@ -7116,13 +7187,13 @@
         <v>133</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="J34" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="2:12">
@@ -7131,7 +7202,7 @@
         <v>1202</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
@@ -7143,16 +7214,16 @@
         <v>2</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="L35" s="2"/>
     </row>
@@ -7162,7 +7233,7 @@
         <v>1203</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E36" s="1">
         <v>1</v>
@@ -7174,16 +7245,16 @@
         <v>2</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="J36" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="L36" s="2"/>
     </row>
@@ -7192,7 +7263,7 @@
         <v>1204</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
@@ -7207,13 +7278,13 @@
         <v>133</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="J37" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="2:12">
@@ -7221,7 +7292,7 @@
         <v>1205</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
@@ -7233,16 +7304,16 @@
         <v>2</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="J38" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="2:12">
@@ -7250,7 +7321,7 @@
         <v>1206</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
@@ -7262,16 +7333,16 @@
         <v>2</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="J39" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="2:12">
@@ -7279,7 +7350,7 @@
         <v>2001</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="E41" s="1">
         <v>1</v>
@@ -7291,16 +7362,16 @@
         <v>2</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="J41" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="2:12">
@@ -7308,7 +7379,7 @@
         <v>2002</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="E42" s="1">
         <v>1</v>
@@ -7320,16 +7391,16 @@
         <v>2</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I42" s="8" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="J42" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="2:12">
@@ -7337,7 +7408,7 @@
         <v>2003</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="E43" s="1">
         <v>1</v>
@@ -7349,16 +7420,16 @@
         <v>2</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="2:12">
@@ -7366,7 +7437,7 @@
         <v>2004</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="E44" s="1">
         <v>1</v>
@@ -7378,16 +7449,16 @@
         <v>2</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="2:12">
@@ -7395,7 +7466,7 @@
         <v>2005</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="E45" s="1">
         <v>1</v>
@@ -7407,16 +7478,16 @@
         <v>2</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="2:12">
@@ -7424,7 +7495,7 @@
         <v>2006</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="E46" s="1">
         <v>1</v>
@@ -7436,16 +7507,16 @@
         <v>2</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="2:12">
@@ -7454,7 +7525,7 @@
         <v>2007</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="E47" s="1">
         <v>1</v>
@@ -7466,16 +7537,16 @@
         <v>2</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="J47" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="L47" s="2"/>
     </row>
@@ -7485,7 +7556,7 @@
         <v>2008</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="E48" s="1">
         <v>1</v>
@@ -7497,16 +7568,16 @@
         <v>2</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="J48" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="L48" s="2"/>
     </row>
@@ -7516,7 +7587,7 @@
         <v>2009</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="E49" s="1">
         <v>1</v>
@@ -7528,16 +7599,16 @@
         <v>2</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="L49" s="2"/>
     </row>
@@ -7547,7 +7618,7 @@
         <v>2010</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="E50" s="1">
         <v>1</v>
@@ -7559,16 +7630,16 @@
         <v>2</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="J50" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="L50" s="2"/>
     </row>
@@ -7578,7 +7649,7 @@
         <v>2011</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="E51" s="1">
         <v>1</v>
@@ -7590,16 +7661,16 @@
         <v>2</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="J51" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="L51" s="2"/>
     </row>
@@ -7609,7 +7680,7 @@
         <v>2012</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="E52" s="1">
         <v>1</v>
@@ -7621,16 +7692,16 @@
         <v>2</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="J52" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="L52" s="2"/>
     </row>
@@ -7652,7 +7723,7 @@
         <v>2013</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="E54" s="1">
         <v>1</v>
@@ -7664,16 +7735,16 @@
         <v>2</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="J54" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K54" s="6" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="L54" s="2"/>
     </row>
@@ -7683,7 +7754,7 @@
         <v>2014</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="E55" s="1">
         <v>1</v>
@@ -7695,16 +7766,16 @@
         <v>2</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="J55" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K55" s="6" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="L55" s="2"/>
     </row>
@@ -7713,7 +7784,7 @@
         <v>2015</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="E56" s="1">
         <v>1</v>
@@ -7725,16 +7796,16 @@
         <v>2</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="J56" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K56" s="6" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="2:12">
@@ -7742,7 +7813,7 @@
         <v>2016</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="E57" s="1">
         <v>1</v>
@@ -7754,16 +7825,16 @@
         <v>2</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="J57" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K57" s="6" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="2:12">
@@ -7771,7 +7842,7 @@
         <v>2017</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="E58" s="1">
         <v>1</v>
@@ -7783,16 +7854,16 @@
         <v>2</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="J58" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K58" s="6" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="2:12">
@@ -7800,7 +7871,7 @@
         <v>2018</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="E59" s="1">
         <v>1</v>
@@ -7812,16 +7883,16 @@
         <v>2</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="J59" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K59" s="6" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="2:12">
@@ -7829,7 +7900,7 @@
         <v>2019</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="E60" s="1">
         <v>1</v>
@@ -7841,16 +7912,16 @@
         <v>2</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I60" s="8" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="J60" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K60" s="6" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="2:12">
@@ -7858,7 +7929,7 @@
         <v>2020</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="E61" s="1">
         <v>1</v>
@@ -7870,16 +7941,16 @@
         <v>2</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="J61" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K61" s="6" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="2:12">
@@ -7887,7 +7958,7 @@
         <v>2021</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="E62" s="1">
         <v>1</v>
@@ -7899,16 +7970,16 @@
         <v>2</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I62" s="8" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="J62" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K62" s="6" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="2:12">
@@ -7916,7 +7987,7 @@
         <v>2022</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E63" s="1">
         <v>1</v>
@@ -7928,16 +7999,16 @@
         <v>2</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="J63" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K63" s="6" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="2:12">
@@ -7945,7 +8016,7 @@
         <v>2023</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="E64" s="1">
         <v>1</v>
@@ -7957,16 +8028,16 @@
         <v>2</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I64" s="8" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="J64" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K64" s="6" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="2:12">
@@ -7974,7 +8045,7 @@
         <v>2024</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="E65" s="1">
         <v>1</v>
@@ -7986,16 +8057,16 @@
         <v>2</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="J65" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K65" s="6" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="2:12">
@@ -8003,7 +8074,7 @@
         <v>2025</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="E66" s="1">
         <v>1</v>
@@ -8015,16 +8086,16 @@
         <v>2</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I66" s="8" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="J66" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K66" s="6" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="2:12">
@@ -8042,7 +8113,7 @@
         <v>2026</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="E68" s="1">
         <v>1</v>
@@ -8054,16 +8125,16 @@
         <v>2</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I68" s="8" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="J68" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K68" s="6" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="2:12">
@@ -8071,7 +8142,7 @@
         <v>2027</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="E69" s="1">
         <v>1</v>
@@ -8083,16 +8154,16 @@
         <v>2</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="J69" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K69" s="6" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="2:12">
@@ -8100,7 +8171,7 @@
         <v>2028</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="E70" s="1">
         <v>1</v>
@@ -8112,16 +8183,16 @@
         <v>2</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="J70" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K70" s="6" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="2:12">
@@ -8129,7 +8200,7 @@
         <v>2029</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="E71" s="1">
         <v>1</v>
@@ -8141,16 +8212,16 @@
         <v>2</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I71" s="8" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="J71" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K71" s="6" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="2:12">
@@ -8158,7 +8229,7 @@
         <v>2030</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="E72" s="1">
         <v>1</v>
@@ -8170,16 +8241,16 @@
         <v>2</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I72" s="8" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="J72" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K72" s="6" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="2:12">
@@ -8187,7 +8258,7 @@
         <v>2031</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="E73" s="1">
         <v>1</v>
@@ -8199,16 +8270,16 @@
         <v>2</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="J73" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K73" s="6" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="2:12">
@@ -8216,7 +8287,7 @@
         <v>2032</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="E74" s="1">
         <v>1</v>
@@ -8228,16 +8299,16 @@
         <v>2</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I74" s="8" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="J74" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K74" s="6" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="2:12">
@@ -8245,7 +8316,7 @@
         <v>2033</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="E75" s="1">
         <v>1</v>
@@ -8257,16 +8328,16 @@
         <v>2</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="J75" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K75" s="6" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="2:12">
@@ -8274,7 +8345,7 @@
         <v>2034</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="E76" s="1">
         <v>1</v>
@@ -8286,16 +8357,16 @@
         <v>2</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I76" s="8" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="J76" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K76" s="6" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="2:12">
@@ -8303,7 +8374,7 @@
         <v>2035</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="E77" s="1">
         <v>1</v>
@@ -8315,16 +8386,16 @@
         <v>2</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="J77" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K77" s="6" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="2:12">
@@ -8332,7 +8403,7 @@
         <v>1301</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E79" s="1">
         <v>1</v>
@@ -8344,16 +8415,16 @@
         <v>2</v>
       </c>
       <c r="H79" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I79" s="8" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="J79" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="80" s="1" customFormat="1" customHeight="1" spans="2:12">
@@ -8362,7 +8433,7 @@
         <v>1302</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="E80" s="1">
         <v>1</v>
@@ -8377,13 +8448,13 @@
         <v>133</v>
       </c>
       <c r="I80" s="8" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="J80" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="L80" s="2"/>
     </row>
@@ -8393,7 +8464,7 @@
         <v>1303</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E81" s="1">
         <v>1</v>
@@ -8405,16 +8476,16 @@
         <v>2</v>
       </c>
       <c r="H81" s="8" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="J81" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="L81" s="2"/>
     </row>
@@ -8423,7 +8494,7 @@
         <v>1304</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="E82" s="1">
         <v>1</v>
@@ -8435,16 +8506,16 @@
         <v>2</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I82" s="8" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="J82" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="2:12">
@@ -8452,7 +8523,7 @@
         <v>1305</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="E83" s="1">
         <v>1</v>
@@ -8464,16 +8535,16 @@
         <v>2</v>
       </c>
       <c r="H83" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I83" s="8" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="J83" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="2:12">
@@ -8481,7 +8552,7 @@
         <v>1306</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="E84" s="1">
         <v>1</v>
@@ -8493,16 +8564,16 @@
         <v>2</v>
       </c>
       <c r="H84" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I84" s="8" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="J84" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="2:12">
@@ -8521,7 +8592,7 @@
         <v>2041</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="E86" s="1">
         <v>1</v>
@@ -8533,16 +8604,16 @@
         <v>2</v>
       </c>
       <c r="H86" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I86" s="8" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="J86" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K86" s="5" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="2:12">
@@ -8550,7 +8621,7 @@
         <v>2042</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E87" s="1">
         <v>1</v>
@@ -8562,16 +8633,16 @@
         <v>2</v>
       </c>
       <c r="H87" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I87" s="8" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="J87" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K87" s="5" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="2:12">
@@ -8579,7 +8650,7 @@
         <v>2043</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="E88" s="1">
         <v>1</v>
@@ -8591,16 +8662,16 @@
         <v>2</v>
       </c>
       <c r="H88" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I88" s="8" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="J88" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K88" s="5" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="2:12">
@@ -8608,7 +8679,7 @@
         <v>2044</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="E89" s="1">
         <v>1</v>
@@ -8620,16 +8691,16 @@
         <v>2</v>
       </c>
       <c r="H89" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I89" s="8" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="J89" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K89" s="5" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="2:12">
@@ -8637,7 +8708,7 @@
         <v>2045</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="E90" s="1">
         <v>1</v>
@@ -8649,16 +8720,16 @@
         <v>2</v>
       </c>
       <c r="H90" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I90" s="8" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="J90" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K90" s="5" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="2:12">
@@ -8666,7 +8737,7 @@
         <v>2046</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="E91" s="1">
         <v>1</v>
@@ -8678,16 +8749,16 @@
         <v>2</v>
       </c>
       <c r="H91" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I91" s="8" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="J91" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K91" s="5" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="2:12">
@@ -8695,7 +8766,7 @@
         <v>2047</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="E92" s="1">
         <v>1</v>
@@ -8707,16 +8778,16 @@
         <v>2</v>
       </c>
       <c r="H92" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I92" s="8" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="J92" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K92" s="5" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="2:12">
@@ -8724,7 +8795,7 @@
         <v>2048</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="E93" s="1">
         <v>1</v>
@@ -8736,16 +8807,16 @@
         <v>2</v>
       </c>
       <c r="H93" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I93" s="8" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="J93" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K93" s="5" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="2:12">
@@ -8753,7 +8824,7 @@
         <v>2049</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="E94" s="1">
         <v>1</v>
@@ -8765,16 +8836,16 @@
         <v>2</v>
       </c>
       <c r="H94" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I94" s="8" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="J94" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K94" s="5" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="2:12">
@@ -8782,7 +8853,7 @@
         <v>2050</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="E95" s="1">
         <v>1</v>
@@ -8794,16 +8865,16 @@
         <v>2</v>
       </c>
       <c r="H95" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I95" s="8" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="J95" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K95" s="5" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="2:12">
@@ -8811,7 +8882,7 @@
         <v>2051</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="E96" s="1">
         <v>1</v>
@@ -8823,16 +8894,16 @@
         <v>2</v>
       </c>
       <c r="H96" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I96" s="8" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="J96" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K96" s="5" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="3:11">
@@ -8843,7 +8914,7 @@
         <v>2052</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="E98" s="1">
         <v>1</v>
@@ -8855,16 +8926,16 @@
         <v>2</v>
       </c>
       <c r="H98" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I98" s="8" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="J98" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K98" s="6" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="3:11">
@@ -8872,7 +8943,7 @@
         <v>2053</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="E99" s="1">
         <v>1</v>
@@ -8884,16 +8955,16 @@
         <v>2</v>
       </c>
       <c r="H99" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I99" s="8" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="J99" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K99" s="6" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="3:11">
@@ -8901,7 +8972,7 @@
         <v>2054</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="E100" s="1">
         <v>1</v>
@@ -8913,16 +8984,16 @@
         <v>2</v>
       </c>
       <c r="H100" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I100" s="8" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="J100" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K100" s="6" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="3:11">
@@ -8930,7 +9001,7 @@
         <v>2055</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="E101" s="1">
         <v>1</v>
@@ -8942,16 +9013,16 @@
         <v>2</v>
       </c>
       <c r="H101" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I101" s="8" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="J101" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K101" s="6" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="3:11">
@@ -8959,7 +9030,7 @@
         <v>2056</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="E102" s="1">
         <v>1</v>
@@ -8971,16 +9042,16 @@
         <v>2</v>
       </c>
       <c r="H102" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I102" s="8" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="J102" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K102" s="6" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="3:11">
@@ -8988,7 +9059,7 @@
         <v>2057</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="E103" s="1">
         <v>1</v>
@@ -9000,16 +9071,16 @@
         <v>2</v>
       </c>
       <c r="H103" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I103" s="8" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="J103" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K103" s="6" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="3:11">
@@ -9017,7 +9088,7 @@
         <v>2058</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="E104" s="1">
         <v>1</v>
@@ -9029,16 +9100,16 @@
         <v>2</v>
       </c>
       <c r="H104" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I104" s="8" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="J104" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K104" s="6" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="3:11">
@@ -9046,7 +9117,7 @@
         <v>2059</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="E105" s="1">
         <v>1</v>
@@ -9058,16 +9129,16 @@
         <v>2</v>
       </c>
       <c r="H105" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I105" s="8" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="J105" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K105" s="6" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="3:11">
@@ -9075,7 +9146,7 @@
         <v>2060</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="E106" s="1">
         <v>1</v>
@@ -9087,16 +9158,16 @@
         <v>2</v>
       </c>
       <c r="H106" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I106" s="8" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="J106" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K106" s="6" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="3:11">
@@ -9104,7 +9175,7 @@
         <v>2061</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="E107" s="1">
         <v>1</v>
@@ -9116,16 +9187,16 @@
         <v>2</v>
       </c>
       <c r="H107" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I107" s="8" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="J107" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K107" s="6" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
     </row>
     <row r="108" customHeight="1" spans="3:11">
@@ -9133,7 +9204,7 @@
         <v>2062</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="E108" s="1">
         <v>1</v>
@@ -9145,16 +9216,16 @@
         <v>2</v>
       </c>
       <c r="H108" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I108" s="8" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="J108" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K108" s="6" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="109" customHeight="1" spans="3:11">
@@ -9165,7 +9236,7 @@
         <v>2063</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="E110" s="1">
         <v>1</v>
@@ -9177,16 +9248,16 @@
         <v>2</v>
       </c>
       <c r="H110" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I110" s="8" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="J110" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K110" s="6" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="3:11">
@@ -9194,7 +9265,7 @@
         <v>2064</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="E111" s="1">
         <v>1</v>
@@ -9206,16 +9277,16 @@
         <v>2</v>
       </c>
       <c r="H111" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I111" s="8" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="J111" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K111" s="6" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
     </row>
     <row r="112" customHeight="1" spans="3:11">
@@ -9223,7 +9294,7 @@
         <v>2065</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="E112" s="1">
         <v>1</v>
@@ -9235,16 +9306,16 @@
         <v>2</v>
       </c>
       <c r="H112" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I112" s="8" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="J112" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K112" s="6" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
     </row>
     <row r="113" customHeight="1" spans="3:11">
@@ -9252,7 +9323,7 @@
         <v>2066</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="E113" s="1">
         <v>1</v>
@@ -9264,16 +9335,16 @@
         <v>2</v>
       </c>
       <c r="H113" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I113" s="8" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="J113" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K113" s="6" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
     </row>
     <row r="114" customHeight="1" spans="3:11">
@@ -9281,7 +9352,7 @@
         <v>2067</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="E114" s="1">
         <v>1</v>
@@ -9293,16 +9364,16 @@
         <v>2</v>
       </c>
       <c r="H114" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I114" s="8" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="J114" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K114" s="6" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
     </row>
     <row r="115" customHeight="1" spans="3:11">
@@ -9310,7 +9381,7 @@
         <v>2068</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="E115" s="1">
         <v>1</v>
@@ -9322,16 +9393,16 @@
         <v>2</v>
       </c>
       <c r="H115" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I115" s="8" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="J115" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K115" s="6" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="116" customHeight="1" spans="3:11">
@@ -9339,7 +9410,7 @@
         <v>2069</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="E116" s="1">
         <v>1</v>
@@ -9351,16 +9422,16 @@
         <v>2</v>
       </c>
       <c r="H116" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I116" s="8" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="J116" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K116" s="6" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
     </row>
     <row r="117" customHeight="1" spans="3:11">
@@ -9368,7 +9439,7 @@
         <v>2070</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="E117" s="1">
         <v>1</v>
@@ -9380,16 +9451,16 @@
         <v>2</v>
       </c>
       <c r="H117" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I117" s="8" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="J117" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K117" s="6" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
     </row>
     <row r="118" customHeight="1" spans="3:11">
@@ -9397,7 +9468,7 @@
         <v>2071</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="E118" s="1">
         <v>1</v>
@@ -9409,16 +9480,16 @@
         <v>2</v>
       </c>
       <c r="H118" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I118" s="8" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="J118" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K118" s="6" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
     </row>
     <row r="119" customHeight="1" spans="3:11">
@@ -9426,7 +9497,7 @@
         <v>2072</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="E119" s="1">
         <v>1</v>
@@ -9438,16 +9509,16 @@
         <v>2</v>
       </c>
       <c r="H119" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I119" s="8" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="J119" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K119" s="6" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="120" customHeight="1" spans="3:11">

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -3625,7 +3625,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" s="8" t="s">
         <v>96</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H34" s="8" t="s">
         <v>30</v>
@@ -6163,7 +6163,7 @@
       <c r="J132" s="1"/>
       <c r="K132" s="1"/>
     </row>
-    <row r="133" spans="3:11">
+    <row r="133" ht="14" spans="3:11">
       <c r="C133" s="1">
         <v>303</v>
       </c>

--- a/Excel/GiftPackConfig.xlsx
+++ b/Excel/GiftPackConfig.xlsx
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1179" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1179" uniqueCount="551">
   <si>
     <t>_id</t>
   </si>
@@ -409,7 +409,13 @@
     <t>极法宝自选</t>
   </si>
   <si>
-    <t>180032,180034,180035,180036,180038,180039</t>
+    <t>18,18,18,18,18,18,18,18,18,18,18</t>
+  </si>
+  <si>
+    <t>180032,180034,180035,180036,180038,180039,180044,180045,180046,180047,180048</t>
+  </si>
+  <si>
+    <t>1,1,1,1,1,1,1,1,1,1,1,1,1</t>
   </si>
   <si>
     <t>普通金宠包</t>
@@ -458,9 +464,6 @@
   </si>
   <si>
     <t>60000001,60000002,60000003,60000004,60000005,60000006,60000007,60000008,60000009,60000010</t>
-  </si>
-  <si>
-    <t>1,1,1,1,1,1,1,1,1,1,1,1,1</t>
   </si>
   <si>
     <t>白虎神器自选</t>
@@ -3715,13 +3718,13 @@
         <v>2</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J36" s="8" t="s">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>105</v>
@@ -3732,7 +3735,7 @@
         <v>32</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E37" s="1">
         <v>0</v>
@@ -3744,16 +3747,16 @@
         <v>2</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J37" s="8" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" customFormat="1" customHeight="1" spans="1:11">
@@ -3761,7 +3764,7 @@
         <v>33</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E38" s="1">
         <v>0</v>
@@ -3773,16 +3776,16 @@
         <v>2</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J38" s="8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="39" customFormat="1" customHeight="1" spans="1:11">
@@ -3792,7 +3795,7 @@
         <v>34</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
@@ -3807,13 +3810,13 @@
         <v>64</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J39" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="40" customFormat="1" customHeight="1" spans="1:11">
@@ -3821,7 +3824,7 @@
         <v>35</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E40" s="1">
         <v>1</v>
@@ -3836,13 +3839,13 @@
         <v>89</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J40" s="8" t="s">
         <v>91</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="41" customFormat="1" customHeight="1" spans="1:11">
@@ -3850,7 +3853,7 @@
         <v>36</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E41" s="1">
         <v>0</v>
@@ -3862,16 +3865,16 @@
         <v>1</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I41" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="J41" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="K41" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="J41" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="42" customFormat="1" customHeight="1" spans="1:11">
@@ -3879,7 +3882,7 @@
         <v>37</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E42" s="1">
         <v>1</v>
@@ -3894,13 +3897,13 @@
         <v>89</v>
       </c>
       <c r="I42" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J42" s="8" t="s">
         <v>91</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="43" customFormat="1" customHeight="1" spans="1:11">
@@ -3908,7 +3911,7 @@
         <v>38</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E43" s="1">
         <v>1</v>
@@ -3923,13 +3926,13 @@
         <v>89</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J43" s="8" t="s">
         <v>91</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="44" customFormat="1" customHeight="1" spans="1:11">
@@ -3937,7 +3940,7 @@
         <v>39</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E44" s="1">
         <v>1</v>
@@ -3952,13 +3955,13 @@
         <v>89</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J44" s="8" t="s">
         <v>91</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="45" customFormat="1" customHeight="1" spans="1:11">
@@ -3966,7 +3969,7 @@
         <v>40</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E45" s="1">
         <v>1</v>
@@ -3981,13 +3984,13 @@
         <v>89</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J45" s="8" t="s">
         <v>91</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="46" customFormat="1" customHeight="1" spans="1:11">
@@ -3995,7 +3998,7 @@
         <v>41</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E46" s="1">
         <v>1</v>
@@ -4007,16 +4010,16 @@
         <v>1</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J46" s="8" t="s">
         <v>91</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="47" customFormat="1" customHeight="1" spans="1:11">
@@ -4024,7 +4027,7 @@
         <v>42</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E47" s="1">
         <v>1</v>
@@ -4039,13 +4042,13 @@
         <v>30</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J47" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="48" customFormat="1" customHeight="1" spans="1:11">
@@ -4055,7 +4058,7 @@
         <v>43</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E48" s="1">
         <v>1</v>
@@ -4067,16 +4070,16 @@
         <v>2</v>
       </c>
       <c r="H48" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="J48" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="K48" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="I48" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="J48" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="K48" s="1" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="1:11">
@@ -4084,7 +4087,7 @@
         <v>44</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E49" s="1">
         <v>1</v>
@@ -4099,13 +4102,13 @@
         <v>77</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J49" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="50" customFormat="1" customHeight="1" spans="1:11">
@@ -4115,7 +4118,7 @@
         <v>46</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E50" s="1">
         <v>1</v>
@@ -4127,16 +4130,16 @@
         <v>2</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I50" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="J50" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="K50" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="J50" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="K50" s="1" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="51" customFormat="1" customHeight="1" spans="1:11">
@@ -4144,7 +4147,7 @@
         <v>47</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E51" s="1">
         <v>1</v>
@@ -4159,13 +4162,13 @@
         <v>89</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J51" s="8" t="s">
         <v>91</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="52" customFormat="1" customHeight="1" spans="1:11">
@@ -4175,7 +4178,7 @@
         <v>48</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E52" s="1">
         <v>1</v>
@@ -4190,13 +4193,13 @@
         <v>89</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J52" s="8" t="s">
         <v>91</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="53" customFormat="1" customHeight="1" spans="1:11">
@@ -4206,7 +4209,7 @@
         <v>49</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E53" s="1">
         <v>1</v>
@@ -4221,13 +4224,13 @@
         <v>89</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J53" s="8" t="s">
         <v>91</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="54" customFormat="1" customHeight="1" spans="1:11">
@@ -4237,7 +4240,7 @@
         <v>50</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E54" s="1">
         <v>1</v>
@@ -4252,13 +4255,13 @@
         <v>89</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J54" s="8" t="s">
         <v>91</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="55" customFormat="1" customHeight="1" spans="1:11">
@@ -4268,7 +4271,7 @@
         <v>51</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E55" s="1">
         <v>1</v>
@@ -4283,13 +4286,13 @@
         <v>89</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J55" s="8" t="s">
         <v>91</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="56" customFormat="1" customHeight="1" spans="1:11">
@@ -4297,7 +4300,7 @@
         <v>52</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E56" s="1">
         <v>1</v>
@@ -4309,16 +4312,16 @@
         <v>1</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J56" s="8" t="s">
         <v>91</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1" spans="1:11">
@@ -4326,7 +4329,7 @@
         <v>53</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E57" s="1">
         <v>1</v>
@@ -4341,13 +4344,13 @@
         <v>77</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J57" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="58" customFormat="1" customHeight="1" spans="1:11">
@@ -4355,7 +4358,7 @@
         <v>54</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E58" s="1">
         <v>0</v>
@@ -4367,16 +4370,16 @@
         <v>1</v>
       </c>
       <c r="H58" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="I58" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="J58" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="K58" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="I58" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="J58" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="59" customFormat="1" customHeight="1" spans="1:11">
@@ -4386,7 +4389,7 @@
         <v>55</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E59" s="1">
         <v>1</v>
@@ -4398,16 +4401,16 @@
         <v>2</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I59" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="J59" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="K59" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="J59" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="K59" s="1" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="60" customFormat="1" customHeight="1" spans="1:11">
@@ -4430,7 +4433,7 @@
         <v>88</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E61" s="1">
         <v>1</v>
@@ -4442,16 +4445,16 @@
         <v>2</v>
       </c>
       <c r="H61" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="I61" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="J61" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="K61" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="I61" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="J61" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="62" customFormat="1" customHeight="1" spans="1:11">
@@ -4461,7 +4464,7 @@
         <v>89</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E62" s="1">
         <v>1</v>
@@ -4473,16 +4476,16 @@
         <v>2</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I62" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="J62" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="K62" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="J62" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="K62" s="1" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="63" customFormat="1" customHeight="1" spans="1:11">
@@ -4492,7 +4495,7 @@
         <v>90</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E63" s="1">
         <v>1</v>
@@ -4504,16 +4507,16 @@
         <v>2</v>
       </c>
       <c r="H63" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="I63" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="J63" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="K63" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="I63" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="J63" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="K63" s="1" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="64" customFormat="1" customHeight="1" spans="1:11">
@@ -4523,7 +4526,7 @@
         <v>91</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E64" s="1">
         <v>1</v>
@@ -4535,16 +4538,16 @@
         <v>2</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I64" s="8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J64" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="65" customFormat="1" customHeight="1" spans="1:11">
@@ -4554,7 +4557,7 @@
         <v>94</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E65" s="1">
         <v>1</v>
@@ -4566,16 +4569,16 @@
         <v>2</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J65" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="66" customFormat="1" customHeight="1" spans="1:11">
@@ -4585,7 +4588,7 @@
         <v>95</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E66" s="1">
         <v>1</v>
@@ -4597,16 +4600,16 @@
         <v>2</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I66" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J66" s="8" t="s">
         <v>91</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="67" customFormat="1" customHeight="1" spans="1:11">
@@ -4614,7 +4617,7 @@
         <v>96</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E67" s="1">
         <v>0</v>
@@ -4626,16 +4629,16 @@
         <v>2</v>
       </c>
       <c r="H67" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="I67" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="J67" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="K67" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="I67" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="J67" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="68" customFormat="1" customHeight="1" spans="1:11">
@@ -4643,7 +4646,7 @@
         <v>97</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E68" s="1">
         <v>1</v>
@@ -4655,16 +4658,16 @@
         <v>2</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I68" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J68" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="69" customFormat="1" customHeight="1" spans="1:11">
@@ -4672,7 +4675,7 @@
         <v>98</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E69" s="1">
         <v>1</v>
@@ -4684,16 +4687,16 @@
         <v>2</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J69" s="8" t="s">
         <v>91</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="70" customFormat="1" customHeight="1" spans="1:11">
@@ -4701,7 +4704,7 @@
         <v>99</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E70" s="1">
         <v>0</v>
@@ -4713,16 +4716,16 @@
         <v>2</v>
       </c>
       <c r="H70" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="I70" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="J70" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="K70" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="I70" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="J70" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="K70" s="1" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="71" customFormat="1" customHeight="1" spans="1:11">
@@ -4730,7 +4733,7 @@
         <v>100</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E71" s="1">
         <v>0</v>
@@ -4742,16 +4745,16 @@
         <v>2</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I71" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="J71" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="K71" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="J71" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="K71" s="1" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="72" customFormat="1" customHeight="1" spans="1:11">
@@ -4759,7 +4762,7 @@
         <v>101</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E72" s="1">
         <v>0</v>
@@ -4771,16 +4774,16 @@
         <v>2</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I72" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="J72" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="K72" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="J72" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="K72" s="1" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="73" customFormat="1" customHeight="1" spans="1:11">
@@ -4788,7 +4791,7 @@
         <v>102</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E73" s="1">
         <v>0</v>
@@ -4800,16 +4803,16 @@
         <v>2</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I73" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="J73" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="K73" s="1" t="s">
         <v>200</v>
-      </c>
-      <c r="J73" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="K73" s="1" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="74" customFormat="1" customHeight="1" spans="1:11">
@@ -4817,7 +4820,7 @@
         <v>103</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E74" s="1">
         <v>0</v>
@@ -4829,16 +4832,16 @@
         <v>2</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I74" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="J74" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="K74" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="J74" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="K74" s="1" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="75" customFormat="1" customHeight="1" spans="1:11">
@@ -4846,7 +4849,7 @@
         <v>104</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E75" s="1">
         <v>0</v>
@@ -4858,16 +4861,16 @@
         <v>2</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I75" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="J75" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="K75" s="1" t="s">
         <v>204</v>
-      </c>
-      <c r="J75" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="K75" s="1" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="76" customFormat="1" customHeight="1" spans="1:11">
@@ -4875,7 +4878,7 @@
         <v>105</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E76" s="1">
         <v>0</v>
@@ -4887,16 +4890,16 @@
         <v>2</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I76" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="J76" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="K76" s="1" t="s">
         <v>206</v>
-      </c>
-      <c r="J76" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="K76" s="1" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="77" ht="14"/>
@@ -4905,7 +4908,7 @@
         <v>106</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E78" s="1">
         <v>1</v>
@@ -4917,16 +4920,16 @@
         <v>1</v>
       </c>
       <c r="H78" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I78" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J78" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="79" customFormat="1" customHeight="1" spans="1:11">
@@ -4934,7 +4937,7 @@
         <v>107</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E79" s="1">
         <v>1</v>
@@ -4949,7 +4952,7 @@
         <v>64</v>
       </c>
       <c r="I79" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J79" s="8" t="s">
         <v>40</v>
@@ -4963,7 +4966,7 @@
         <v>108</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E80" s="1">
         <v>1</v>
@@ -4978,13 +4981,13 @@
         <v>64</v>
       </c>
       <c r="I80" s="8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J80" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="81" ht="14"/>
@@ -4993,7 +4996,7 @@
         <v>109</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E82" s="1">
         <v>1</v>
@@ -5005,16 +5008,16 @@
         <v>2</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I82" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J82" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="83" customFormat="1" customHeight="1" spans="1:11">
@@ -5022,7 +5025,7 @@
         <v>110</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E83" s="1">
         <v>1</v>
@@ -5034,16 +5037,16 @@
         <v>2</v>
       </c>
       <c r="H83" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I83" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J83" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="84" customFormat="1" customHeight="1" spans="1:11">
@@ -5051,7 +5054,7 @@
         <v>111</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E84" s="1">
         <v>1</v>
@@ -5063,16 +5066,16 @@
         <v>2</v>
       </c>
       <c r="H84" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I84" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J84" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="85" customFormat="1" customHeight="1" spans="1:11">
@@ -5080,7 +5083,7 @@
         <v>112</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E85" s="1">
         <v>1</v>
@@ -5092,16 +5095,16 @@
         <v>2</v>
       </c>
       <c r="H85" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I85" s="8" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J85" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" customFormat="1" customHeight="1" spans="1:11">
@@ -5109,7 +5112,7 @@
         <v>113</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E86" s="1">
         <v>1</v>
@@ -5121,16 +5124,16 @@
         <v>2</v>
       </c>
       <c r="H86" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I86" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J86" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="87" customFormat="1" customHeight="1" spans="1:11">
@@ -5138,7 +5141,7 @@
         <v>114</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E87" s="1">
         <v>1</v>
@@ -5150,16 +5153,16 @@
         <v>2</v>
       </c>
       <c r="H87" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I87" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="J87" s="8" t="s">
         <v>91</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="88" customFormat="1" customHeight="1" spans="1:11">
@@ -5167,7 +5170,7 @@
         <v>115</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E88" s="1">
         <v>1</v>
@@ -5179,31 +5182,31 @@
         <v>2</v>
       </c>
       <c r="H88" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I88" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J88" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="89" ht="14"/>
     <row r="90" customFormat="1" customHeight="1" spans="1:11">
       <c r="A90" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C90" s="1">
         <v>118</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E90" s="1">
         <v>1</v>
@@ -5215,30 +5218,30 @@
         <v>2</v>
       </c>
       <c r="H90" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I90" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J90" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K90" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="91" customFormat="1" customHeight="1" spans="1:11">
       <c r="A91" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C91" s="1">
         <v>119</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E91" s="1">
         <v>1</v>
@@ -5250,30 +5253,30 @@
         <v>2</v>
       </c>
       <c r="H91" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I91" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J91" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K91" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="92" customFormat="1" customHeight="1" spans="1:11">
       <c r="A92" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C92" s="1">
         <v>120</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E92" s="1">
         <v>1</v>
@@ -5285,30 +5288,30 @@
         <v>2</v>
       </c>
       <c r="H92" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I92" s="8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J92" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K92" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="93" customFormat="1" customHeight="1" spans="1:11">
       <c r="A93" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C93" s="1">
         <v>121</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E93" s="1">
         <v>1</v>
@@ -5320,30 +5323,30 @@
         <v>2</v>
       </c>
       <c r="H93" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I93" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J93" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K93" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="94" customFormat="1" customHeight="1" spans="1:11">
       <c r="A94" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C94" s="1">
         <v>122</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E94" s="1">
         <v>1</v>
@@ -5355,30 +5358,30 @@
         <v>2</v>
       </c>
       <c r="H94" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I94" s="8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J94" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="95" customFormat="1" customHeight="1" spans="1:11">
       <c r="A95" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C95" s="1">
         <v>123</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E95" s="1">
         <v>1</v>
@@ -5390,30 +5393,30 @@
         <v>2</v>
       </c>
       <c r="H95" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I95" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J95" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K95" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="96" customFormat="1" customHeight="1" spans="1:11">
       <c r="A96" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C96" s="1">
         <v>124</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E96" s="1">
         <v>1</v>
@@ -5425,30 +5428,30 @@
         <v>2</v>
       </c>
       <c r="H96" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I96" s="8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J96" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="97" customFormat="1" customHeight="1" spans="1:11">
       <c r="A97" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C97" s="1">
         <v>125</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E97" s="1">
         <v>1</v>
@@ -5460,30 +5463,30 @@
         <v>2</v>
       </c>
       <c r="H97" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I97" s="8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J97" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="98" customFormat="1" customHeight="1" spans="1:11">
       <c r="A98" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C98" s="1">
         <v>126</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E98" s="1">
         <v>1</v>
@@ -5495,30 +5498,30 @@
         <v>2</v>
       </c>
       <c r="H98" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I98" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J98" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="99" customFormat="1" customHeight="1" spans="1:11">
       <c r="A99" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C99" s="1">
         <v>127</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E99" s="1">
         <v>1</v>
@@ -5530,30 +5533,30 @@
         <v>2</v>
       </c>
       <c r="H99" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I99" s="8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J99" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="100" customFormat="1" customHeight="1" spans="1:11">
       <c r="A100" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C100" s="1">
         <v>128</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E100" s="1">
         <v>1</v>
@@ -5565,30 +5568,30 @@
         <v>2</v>
       </c>
       <c r="H100" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I100" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J100" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="101" customFormat="1" customHeight="1" spans="1:11">
       <c r="A101" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C101" s="1">
         <v>129</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E101" s="1">
         <v>1</v>
@@ -5600,30 +5603,30 @@
         <v>2</v>
       </c>
       <c r="H101" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I101" s="8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="J101" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="102" customFormat="1" customHeight="1" spans="1:11">
       <c r="A102" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C102" s="1">
         <v>130</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E102" s="1">
         <v>1</v>
@@ -5635,30 +5638,30 @@
         <v>2</v>
       </c>
       <c r="H102" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I102" s="8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J102" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="103" customFormat="1" customHeight="1" spans="1:11">
       <c r="A103" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C103" s="1">
         <v>131</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E103" s="1">
         <v>1</v>
@@ -5670,31 +5673,31 @@
         <v>2</v>
       </c>
       <c r="H103" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I103" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J103" s="8" t="s">
         <v>87</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="104" ht="14"/>
     <row r="105" customFormat="1" customHeight="1" spans="1:11">
       <c r="A105" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C105" s="1">
         <v>137</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E105" s="1">
         <v>1</v>
@@ -5706,30 +5709,30 @@
         <v>2</v>
       </c>
       <c r="H105" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I105" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="J105" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="106" customFormat="1" customHeight="1" spans="1:11">
       <c r="A106" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C106" s="1">
         <v>138</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E106" s="1">
         <v>1</v>
@@ -5741,51 +5744,51 @@
         <v>2</v>
       </c>
       <c r="H106" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="I106" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="J106" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="K106" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="I106" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="J106" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="K106" s="1" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="107" customFormat="1" customHeight="1" spans="1:11">
       <c r="A107" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C107" s="1">
         <v>139</v>
       </c>
       <c r="D107" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E107" s="1">
+        <v>1</v>
+      </c>
+      <c r="F107" s="4">
+        <v>0</v>
+      </c>
+      <c r="G107" s="4">
+        <v>2</v>
+      </c>
+      <c r="H107" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="I107" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="J107" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="E107" s="1">
-        <v>1</v>
-      </c>
-      <c r="F107" s="4">
-        <v>0</v>
-      </c>
-      <c r="G107" s="4">
-        <v>2</v>
-      </c>
-      <c r="H107" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="I107" s="8" t="s">
+      <c r="K107" s="1" t="s">
         <v>275</v>
-      </c>
-      <c r="J107" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="K107" s="1" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="108" ht="14"/>
@@ -5802,7 +5805,7 @@
         <v>201</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E117" s="1">
         <v>1</v>
@@ -5814,16 +5817,16 @@
         <v>2</v>
       </c>
       <c r="H117" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I117" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J117" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="118" customFormat="1" customHeight="1" spans="3:11">
@@ -5831,7 +5834,7 @@
         <v>202</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E118" s="1">
         <v>1</v>
@@ -5843,16 +5846,16 @@
         <v>2</v>
       </c>
       <c r="H118" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I118" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J118" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="119" customFormat="1" customHeight="1" spans="3:11">
@@ -5860,7 +5863,7 @@
         <v>203</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E119" s="1">
         <v>1</v>
@@ -5872,16 +5875,16 @@
         <v>2</v>
       </c>
       <c r="H119" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I119" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="J119" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="120" customFormat="1" customHeight="1" spans="3:11">
@@ -5889,7 +5892,7 @@
         <v>204</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E120" s="1">
         <v>1</v>
@@ -5901,16 +5904,16 @@
         <v>2</v>
       </c>
       <c r="H120" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I120" s="8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="J120" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="121" customFormat="1" customHeight="1" spans="3:11">
@@ -5918,7 +5921,7 @@
         <v>205</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E121" s="1">
         <v>1</v>
@@ -5930,16 +5933,16 @@
         <v>2</v>
       </c>
       <c r="H121" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I121" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="J121" s="8" t="s">
         <v>32</v>
       </c>
       <c r="K121" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="122" ht="14"/>
@@ -5948,7 +5951,7 @@
         <v>207</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E123" s="1">
         <v>1</v>
@@ -5960,16 +5963,16 @@
         <v>2</v>
       </c>
       <c r="H123" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I123" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J123" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K123" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="124" customFormat="1" customHeight="1" spans="3:11">
@@ -5977,7 +5980,7 @@
         <v>208</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E124" s="1">
         <v>1</v>
@@ -5989,16 +5992,16 @@
         <v>2</v>
       </c>
       <c r="H124" s="8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I124" s="8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J124" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K124" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="125" customFormat="1" customHeight="1" spans="3:11">
@@ -6006,7 +6009,7 @@
         <v>209</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E125" s="1">
         <v>1</v>
@@ -6018,16 +6021,16 @@
         <v>2</v>
       </c>
       <c r="H125" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I125" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J125" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="126" customFormat="1" customHeight="1" spans="3:11">
@@ -6035,28 +6038,28 @@
         <v>210</v>
       </c>
       <c r="D126" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="E126" s="1">
+        <v>1</v>
+      </c>
+      <c r="F126" s="4">
+        <v>0</v>
+      </c>
+      <c r="G126" s="4">
+        <v>2</v>
+      </c>
+      <c r="H126" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="I126" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="J126" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K126" s="1" t="s">
         <v>303</v>
-      </c>
-      <c r="E126" s="1">
-        <v>1</v>
-      </c>
-      <c r="F126" s="4">
-        <v>0</v>
-      </c>
-      <c r="G126" s="4">
-        <v>2</v>
-      </c>
-      <c r="H126" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="I126" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="J126" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="K126" s="1" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="127" customFormat="1" customHeight="1" spans="3:11">
@@ -6064,7 +6067,7 @@
         <v>211</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E127" s="1">
         <v>1</v>
@@ -6076,16 +6079,16 @@
         <v>2</v>
       </c>
       <c r="H127" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I127" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="J127" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K127" s="1" t="s">
         <v>307</v>
-      </c>
-      <c r="J127" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="K127" s="1" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="128" customFormat="1" customHeight="1" spans="3:11">
@@ -6093,7 +6096,7 @@
         <v>212</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E128" s="1">
         <v>1</v>
@@ -6105,16 +6108,16 @@
         <v>2</v>
       </c>
       <c r="H128" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I128" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="J128" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K128" s="1" t="s">
         <v>309</v>
-      </c>
-      <c r="J128" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="K128" s="1" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="129" ht="14"/>
@@ -6124,7 +6127,7 @@
         <v>301</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E131" s="1">
         <v>1</v>
@@ -6136,16 +6139,16 @@
         <v>2</v>
       </c>
       <c r="H131" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="I131" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="J131" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K131" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="I131" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="J131" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="K131" s="1" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="132" ht="14" spans="3:11">
@@ -6153,7 +6156,7 @@
         <v>302</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E132" s="1"/>
       <c r="F132" s="4"/>
@@ -6168,7 +6171,7 @@
         <v>303</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E133" s="1">
         <v>1</v>
@@ -6180,16 +6183,16 @@
         <v>2</v>
       </c>
       <c r="H133" s="8" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="I133" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="J133" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K133" s="1" t="s">
         <v>315</v>
-      </c>
-      <c r="J133" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="K133" s="1" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="134" customFormat="1" ht="14" spans="3:11">
@@ -6197,7 +6200,7 @@
         <v>304</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E134" s="1">
         <v>1</v>
@@ -6209,16 +6212,16 @@
         <v>2</v>
       </c>
       <c r="H134" s="8" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="I134" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="J134" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K134" s="1" t="s">
         <v>317</v>
-      </c>
-      <c r="J134" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="K134" s="1" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="135" ht="14" spans="3:11">
@@ -6226,7 +6229,7 @@
         <v>305</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E135" s="1">
         <v>1</v>
@@ -6238,16 +6241,16 @@
         <v>2</v>
       </c>
       <c r="H135" s="8" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="I135" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="J135" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K135" s="1" t="s">
         <v>319</v>
-      </c>
-      <c r="J135" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="K135" s="1" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="136" ht="14" spans="3:11">
@@ -6255,7 +6258,7 @@
         <v>306</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E136" s="1">
         <v>1</v>
@@ -6267,16 +6270,16 @@
         <v>2</v>
       </c>
       <c r="H136" s="8" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="I136" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="J136" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K136" s="1" t="s">
         <v>321</v>
-      </c>
-      <c r="J136" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="K136" s="1" t="s">
-        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -6404,7 +6407,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -6419,13 +6422,13 @@
         <v>14</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J6" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6433,7 +6436,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -6448,13 +6451,13 @@
         <v>14</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J7" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6462,7 +6465,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -6477,13 +6480,13 @@
         <v>14</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J8" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6491,7 +6494,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -6506,13 +6509,13 @@
         <v>14</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J9" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6520,7 +6523,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -6535,13 +6538,13 @@
         <v>14</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6549,7 +6552,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -6564,13 +6567,13 @@
         <v>14</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J11" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6578,7 +6581,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -6593,13 +6596,13 @@
         <v>14</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6607,7 +6610,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -6622,13 +6625,13 @@
         <v>14</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J13" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6636,7 +6639,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -6651,13 +6654,13 @@
         <v>14</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J14" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6665,7 +6668,7 @@
         <v>1010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -6680,13 +6683,13 @@
         <v>14</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6694,7 +6697,7 @@
         <v>1011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -6709,13 +6712,13 @@
         <v>14</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="J16" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6723,7 +6726,7 @@
         <v>1012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -6738,13 +6741,13 @@
         <v>14</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="J17" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6752,7 +6755,7 @@
         <v>1013</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -6767,13 +6770,13 @@
         <v>14</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="J18" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6781,7 +6784,7 @@
         <v>1014</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
@@ -6796,13 +6799,13 @@
         <v>14</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J19" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1"/>
@@ -6811,7 +6814,7 @@
         <v>1101</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -6826,13 +6829,13 @@
         <v>14</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="J21" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6840,7 +6843,7 @@
         <v>1102</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -6855,13 +6858,13 @@
         <v>14</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J22" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6869,7 +6872,7 @@
         <v>1103</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -6884,13 +6887,13 @@
         <v>14</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="J23" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6898,7 +6901,7 @@
         <v>1104</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -6913,13 +6916,13 @@
         <v>14</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J24" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6927,7 +6930,7 @@
         <v>1105</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -6942,13 +6945,13 @@
         <v>14</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="J25" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6956,7 +6959,7 @@
         <v>1106</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -6971,13 +6974,13 @@
         <v>14</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J26" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -6985,7 +6988,7 @@
         <v>1107</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -7000,13 +7003,13 @@
         <v>14</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="J27" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -7014,7 +7017,7 @@
         <v>1108</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
@@ -7029,13 +7032,13 @@
         <v>14</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J28" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -7043,7 +7046,7 @@
         <v>1109</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -7058,13 +7061,13 @@
         <v>14</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J29" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -7072,7 +7075,7 @@
         <v>1110</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -7087,13 +7090,13 @@
         <v>14</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J30" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -7101,7 +7104,7 @@
         <v>1111</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -7116,13 +7119,13 @@
         <v>14</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J31" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -7130,7 +7133,7 @@
         <v>1112</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -7145,13 +7148,13 @@
         <v>14</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J32" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="2:12">
@@ -7172,7 +7175,7 @@
         <v>1201</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
@@ -7184,16 +7187,16 @@
         <v>2</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J34" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="2:12">
@@ -7202,7 +7205,7 @@
         <v>1202</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
@@ -7214,16 +7217,16 @@
         <v>2</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L35" s="2"/>
     </row>
@@ -7233,7 +7236,7 @@
         <v>1203</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E36" s="1">
         <v>1</v>
@@ -7245,16 +7248,16 @@
         <v>2</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="J36" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L36" s="2"/>
     </row>
@@ -7263,7 +7266,7 @@
         <v>1204</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
@@ -7275,16 +7278,16 @@
         <v>2</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="J37" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="2:12">
@@ -7292,7 +7295,7 @@
         <v>1205</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
@@ -7304,16 +7307,16 @@
         <v>2</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="J38" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="2:12">
@@ -7321,7 +7324,7 @@
         <v>1206</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
@@ -7333,16 +7336,16 @@
         <v>2</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="J39" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="2:12">
@@ -7350,7 +7353,7 @@
         <v>2001</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E41" s="1">
         <v>1</v>
@@ -7362,16 +7365,16 @@
         <v>2</v>
       </c>
       <c r="H41" s="8" t="s">
+        <v>418</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="J41" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K41" s="5" t="s">
         <v>417</v>
-      </c>
-      <c r="I41" s="8" t="s">
-        <v>418</v>
-      </c>
-      <c r="J41" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K41" s="5" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="2:12">
@@ -7379,7 +7382,7 @@
         <v>2002</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E42" s="1">
         <v>1</v>
@@ -7391,16 +7394,16 @@
         <v>2</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I42" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="J42" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K42" s="5" t="s">
         <v>420</v>
-      </c>
-      <c r="J42" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K42" s="5" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="2:12">
@@ -7408,7 +7411,7 @@
         <v>2003</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E43" s="1">
         <v>1</v>
@@ -7420,16 +7423,16 @@
         <v>2</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I43" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="J43" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K43" s="5" t="s">
         <v>422</v>
-      </c>
-      <c r="J43" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K43" s="5" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="2:12">
@@ -7437,7 +7440,7 @@
         <v>2004</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E44" s="1">
         <v>1</v>
@@ -7449,16 +7452,16 @@
         <v>2</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I44" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="J44" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K44" s="5" t="s">
         <v>424</v>
-      </c>
-      <c r="J44" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K44" s="5" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="2:12">
@@ -7466,7 +7469,7 @@
         <v>2005</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E45" s="1">
         <v>1</v>
@@ -7478,16 +7481,16 @@
         <v>2</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I45" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="J45" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K45" s="5" t="s">
         <v>426</v>
-      </c>
-      <c r="J45" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K45" s="5" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="2:12">
@@ -7495,7 +7498,7 @@
         <v>2006</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E46" s="1">
         <v>1</v>
@@ -7507,16 +7510,16 @@
         <v>2</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I46" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="J46" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K46" s="5" t="s">
         <v>428</v>
-      </c>
-      <c r="J46" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K46" s="5" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="2:12">
@@ -7525,7 +7528,7 @@
         <v>2007</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E47" s="1">
         <v>1</v>
@@ -7537,16 +7540,16 @@
         <v>2</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I47" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="J47" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K47" s="5" t="s">
         <v>430</v>
-      </c>
-      <c r="J47" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K47" s="5" t="s">
-        <v>429</v>
       </c>
       <c r="L47" s="2"/>
     </row>
@@ -7556,7 +7559,7 @@
         <v>2008</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E48" s="1">
         <v>1</v>
@@ -7568,16 +7571,16 @@
         <v>2</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I48" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="J48" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K48" s="5" t="s">
         <v>432</v>
-      </c>
-      <c r="J48" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K48" s="5" t="s">
-        <v>431</v>
       </c>
       <c r="L48" s="2"/>
     </row>
@@ -7587,7 +7590,7 @@
         <v>2009</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E49" s="1">
         <v>1</v>
@@ -7599,16 +7602,16 @@
         <v>2</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I49" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="J49" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K49" s="5" t="s">
         <v>434</v>
-      </c>
-      <c r="J49" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K49" s="5" t="s">
-        <v>433</v>
       </c>
       <c r="L49" s="2"/>
     </row>
@@ -7618,7 +7621,7 @@
         <v>2010</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E50" s="1">
         <v>1</v>
@@ -7630,16 +7633,16 @@
         <v>2</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I50" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="J50" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K50" s="5" t="s">
         <v>436</v>
-      </c>
-      <c r="J50" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K50" s="5" t="s">
-        <v>435</v>
       </c>
       <c r="L50" s="2"/>
     </row>
@@ -7649,7 +7652,7 @@
         <v>2011</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E51" s="1">
         <v>1</v>
@@ -7661,16 +7664,16 @@
         <v>2</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I51" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="J51" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K51" s="5" t="s">
         <v>438</v>
-      </c>
-      <c r="J51" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K51" s="5" t="s">
-        <v>437</v>
       </c>
       <c r="L51" s="2"/>
     </row>
@@ -7680,7 +7683,7 @@
         <v>2012</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E52" s="1">
         <v>1</v>
@@ -7692,16 +7695,16 @@
         <v>2</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I52" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="J52" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K52" s="5" t="s">
         <v>440</v>
-      </c>
-      <c r="J52" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K52" s="5" t="s">
-        <v>439</v>
       </c>
       <c r="L52" s="2"/>
     </row>
@@ -7723,7 +7726,7 @@
         <v>2013</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E54" s="1">
         <v>1</v>
@@ -7735,16 +7738,16 @@
         <v>2</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I54" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="J54" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K54" s="6" t="s">
         <v>442</v>
-      </c>
-      <c r="J54" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K54" s="6" t="s">
-        <v>441</v>
       </c>
       <c r="L54" s="2"/>
     </row>
@@ -7754,7 +7757,7 @@
         <v>2014</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E55" s="1">
         <v>1</v>
@@ -7766,16 +7769,16 @@
         <v>2</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I55" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="J55" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K55" s="6" t="s">
         <v>444</v>
-      </c>
-      <c r="J55" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K55" s="6" t="s">
-        <v>443</v>
       </c>
       <c r="L55" s="2"/>
     </row>
@@ -7784,7 +7787,7 @@
         <v>2015</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E56" s="1">
         <v>1</v>
@@ -7796,16 +7799,16 @@
         <v>2</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I56" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="J56" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K56" s="6" t="s">
         <v>446</v>
-      </c>
-      <c r="J56" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K56" s="6" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="2:12">
@@ -7813,7 +7816,7 @@
         <v>2016</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E57" s="1">
         <v>1</v>
@@ -7825,16 +7828,16 @@
         <v>2</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I57" s="8" t="s">
+        <v>449</v>
+      </c>
+      <c r="J57" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K57" s="6" t="s">
         <v>448</v>
-      </c>
-      <c r="J57" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K57" s="6" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="2:12">
@@ -7842,7 +7845,7 @@
         <v>2017</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E58" s="1">
         <v>1</v>
@@ -7854,16 +7857,16 @@
         <v>2</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I58" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="J58" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K58" s="6" t="s">
         <v>450</v>
-      </c>
-      <c r="J58" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K58" s="6" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="2:12">
@@ -7871,7 +7874,7 @@
         <v>2018</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E59" s="1">
         <v>1</v>
@@ -7883,16 +7886,16 @@
         <v>2</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I59" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="J59" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K59" s="6" t="s">
         <v>452</v>
-      </c>
-      <c r="J59" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K59" s="6" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="2:12">
@@ -7900,7 +7903,7 @@
         <v>2019</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E60" s="1">
         <v>1</v>
@@ -7912,16 +7915,16 @@
         <v>2</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I60" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="J60" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K60" s="6" t="s">
         <v>454</v>
-      </c>
-      <c r="J60" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K60" s="6" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="2:12">
@@ -7929,7 +7932,7 @@
         <v>2020</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E61" s="1">
         <v>1</v>
@@ -7941,16 +7944,16 @@
         <v>2</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I61" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="J61" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K61" s="6" t="s">
         <v>456</v>
-      </c>
-      <c r="J61" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K61" s="6" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="2:12">
@@ -7958,7 +7961,7 @@
         <v>2021</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E62" s="1">
         <v>1</v>
@@ -7970,16 +7973,16 @@
         <v>2</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I62" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="J62" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K62" s="6" t="s">
         <v>458</v>
-      </c>
-      <c r="J62" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K62" s="6" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="2:12">
@@ -7987,7 +7990,7 @@
         <v>2022</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E63" s="1">
         <v>1</v>
@@ -7999,16 +8002,16 @@
         <v>2</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I63" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="J63" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K63" s="6" t="s">
         <v>460</v>
-      </c>
-      <c r="J63" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K63" s="6" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="2:12">
@@ -8016,7 +8019,7 @@
         <v>2023</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E64" s="1">
         <v>1</v>
@@ -8028,16 +8031,16 @@
         <v>2</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I64" s="8" t="s">
+        <v>463</v>
+      </c>
+      <c r="J64" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K64" s="6" t="s">
         <v>462</v>
-      </c>
-      <c r="J64" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K64" s="6" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="2:12">
@@ -8045,7 +8048,7 @@
         <v>2024</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E65" s="1">
         <v>1</v>
@@ -8057,16 +8060,16 @@
         <v>2</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I65" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="J65" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K65" s="6" t="s">
         <v>464</v>
-      </c>
-      <c r="J65" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K65" s="6" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="2:12">
@@ -8074,7 +8077,7 @@
         <v>2025</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E66" s="1">
         <v>1</v>
@@ -8086,16 +8089,16 @@
         <v>2</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I66" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="J66" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K66" s="6" t="s">
         <v>466</v>
-      </c>
-      <c r="J66" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K66" s="6" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="2:12">
@@ -8113,7 +8116,7 @@
         <v>2026</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E68" s="1">
         <v>1</v>
@@ -8125,16 +8128,16 @@
         <v>2</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I68" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="J68" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K68" s="6" t="s">
         <v>468</v>
-      </c>
-      <c r="J68" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K68" s="6" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="2:12">
@@ -8142,7 +8145,7 @@
         <v>2027</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E69" s="1">
         <v>1</v>
@@ -8154,16 +8157,16 @@
         <v>2</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I69" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="J69" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K69" s="6" t="s">
         <v>470</v>
-      </c>
-      <c r="J69" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K69" s="6" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="2:12">
@@ -8171,7 +8174,7 @@
         <v>2028</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E70" s="1">
         <v>1</v>
@@ -8183,16 +8186,16 @@
         <v>2</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I70" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="J70" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K70" s="6" t="s">
         <v>472</v>
-      </c>
-      <c r="J70" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K70" s="6" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="2:12">
@@ -8200,7 +8203,7 @@
         <v>2029</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E71" s="1">
         <v>1</v>
@@ -8212,16 +8215,16 @@
         <v>2</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I71" s="8" t="s">
+        <v>475</v>
+      </c>
+      <c r="J71" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K71" s="6" t="s">
         <v>474</v>
-      </c>
-      <c r="J71" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K71" s="6" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="2:12">
@@ -8229,7 +8232,7 @@
         <v>2030</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E72" s="1">
         <v>1</v>
@@ -8241,16 +8244,16 @@
         <v>2</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I72" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="J72" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K72" s="6" t="s">
         <v>476</v>
-      </c>
-      <c r="J72" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K72" s="6" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="2:12">
@@ -8258,7 +8261,7 @@
         <v>2031</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E73" s="1">
         <v>1</v>
@@ -8270,16 +8273,16 @@
         <v>2</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I73" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="J73" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K73" s="6" t="s">
         <v>478</v>
-      </c>
-      <c r="J73" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K73" s="6" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="2:12">
@@ -8287,7 +8290,7 @@
         <v>2032</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E74" s="1">
         <v>1</v>
@@ -8299,16 +8302,16 @@
         <v>2</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I74" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="J74" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K74" s="6" t="s">
         <v>480</v>
-      </c>
-      <c r="J74" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K74" s="6" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="2:12">
@@ -8316,7 +8319,7 @@
         <v>2033</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E75" s="1">
         <v>1</v>
@@ -8328,16 +8331,16 @@
         <v>2</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I75" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="J75" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K75" s="6" t="s">
         <v>482</v>
-      </c>
-      <c r="J75" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K75" s="6" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="2:12">
@@ -8345,7 +8348,7 @@
         <v>2034</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E76" s="1">
         <v>1</v>
@@ -8357,16 +8360,16 @@
         <v>2</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I76" s="8" t="s">
+        <v>485</v>
+      </c>
+      <c r="J76" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K76" s="6" t="s">
         <v>484</v>
-      </c>
-      <c r="J76" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K76" s="6" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="2:12">
@@ -8374,7 +8377,7 @@
         <v>2035</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E77" s="1">
         <v>1</v>
@@ -8386,16 +8389,16 @@
         <v>2</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I77" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="J77" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K77" s="6" t="s">
         <v>486</v>
-      </c>
-      <c r="J77" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K77" s="6" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="2:12">
@@ -8403,7 +8406,7 @@
         <v>1301</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E79" s="1">
         <v>1</v>
@@ -8415,16 +8418,16 @@
         <v>2</v>
       </c>
       <c r="H79" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I79" s="8" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="J79" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="80" s="1" customFormat="1" customHeight="1" spans="2:12">
@@ -8433,7 +8436,7 @@
         <v>1302</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E80" s="1">
         <v>1</v>
@@ -8445,16 +8448,16 @@
         <v>2</v>
       </c>
       <c r="H80" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I80" s="8" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="J80" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L80" s="2"/>
     </row>
@@ -8464,7 +8467,7 @@
         <v>1303</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E81" s="1">
         <v>1</v>
@@ -8476,16 +8479,16 @@
         <v>2</v>
       </c>
       <c r="H81" s="8" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="J81" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L81" s="2"/>
     </row>
@@ -8494,7 +8497,7 @@
         <v>1304</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E82" s="1">
         <v>1</v>
@@ -8506,16 +8509,16 @@
         <v>2</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I82" s="8" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J82" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="2:12">
@@ -8523,7 +8526,7 @@
         <v>1305</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E83" s="1">
         <v>1</v>
@@ -8535,16 +8538,16 @@
         <v>2</v>
       </c>
       <c r="H83" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I83" s="8" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="J83" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="2:12">
@@ -8552,7 +8555,7 @@
         <v>1306</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E84" s="1">
         <v>1</v>
@@ -8564,16 +8567,16 @@
         <v>2</v>
       </c>
       <c r="H84" s="8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I84" s="8" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="J84" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="2:12">
@@ -8592,7 +8595,7 @@
         <v>2041</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E86" s="1">
         <v>1</v>
@@ -8604,16 +8607,16 @@
         <v>2</v>
       </c>
       <c r="H86" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I86" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="J86" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K86" s="5" t="s">
         <v>494</v>
-      </c>
-      <c r="J86" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K86" s="5" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="2:12">
@@ -8621,7 +8624,7 @@
         <v>2042</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E87" s="1">
         <v>1</v>
@@ -8633,16 +8636,16 @@
         <v>2</v>
       </c>
       <c r="H87" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I87" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="J87" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K87" s="5" t="s">
         <v>496</v>
-      </c>
-      <c r="J87" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K87" s="5" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="2:12">
@@ -8650,7 +8653,7 @@
         <v>2043</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E88" s="1">
         <v>1</v>
@@ -8662,16 +8665,16 @@
         <v>2</v>
       </c>
       <c r="H88" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I88" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="J88" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K88" s="5" t="s">
         <v>498</v>
-      </c>
-      <c r="J88" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K88" s="5" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="2:12">
@@ -8679,7 +8682,7 @@
         <v>2044</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E89" s="1">
         <v>1</v>
@@ -8691,16 +8694,16 @@
         <v>2</v>
       </c>
       <c r="H89" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I89" s="8" t="s">
+        <v>501</v>
+      </c>
+      <c r="J89" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K89" s="5" t="s">
         <v>500</v>
-      </c>
-      <c r="J89" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K89" s="5" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="2:12">
@@ -8708,7 +8711,7 @@
         <v>2045</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E90" s="1">
         <v>1</v>
@@ -8720,16 +8723,16 @@
         <v>2</v>
       </c>
       <c r="H90" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I90" s="8" t="s">
+        <v>503</v>
+      </c>
+      <c r="J90" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K90" s="5" t="s">
         <v>502</v>
-      </c>
-      <c r="J90" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K90" s="5" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="2:12">
@@ -8737,7 +8740,7 @@
         <v>2046</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E91" s="1">
         <v>1</v>
@@ -8749,16 +8752,16 @@
         <v>2</v>
       </c>
       <c r="H91" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I91" s="8" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="J91" s="8" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K91" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="2:12">
@@ -8766,7 +8769,7 @@
         <v>2047</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E92" s="1">
         <v>1</v>
@@ -8778,16 +8781,16 @@
         <v>2</v>
       </c>
       <c r="H92" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I92" s="8" t="s">
+        <v>506</v>
+      </c>
+      <c r="J92" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K92" s="5" t="s">
         <v>505</v>
-      </c>
-      <c r="J92" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K92" s="5" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="2:12">
@@ -8795,7 +8798,7 @@
         <v>2048</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E93" s="1">
         <v>1</v>
@@ -8807,16 +8810,16 @@
         <v>2</v>
       </c>
       <c r="H93" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I93" s="8" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="J93" s="8" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K93" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="2:12">
@@ -8824,7 +8827,7 @@
         <v>2049</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E94" s="1">
         <v>1</v>
@@ -8836,16 +8839,16 @@
         <v>2</v>
       </c>
       <c r="H94" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I94" s="8" t="s">
+        <v>509</v>
+      </c>
+      <c r="J94" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K94" s="5" t="s">
         <v>508</v>
-      </c>
-      <c r="J94" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K94" s="5" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="2:12">
@@ -8853,7 +8856,7 @@
         <v>2050</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E95" s="1">
         <v>1</v>
@@ -8865,16 +8868,16 @@
         <v>2</v>
       </c>
       <c r="H95" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I95" s="8" t="s">
+        <v>511</v>
+      </c>
+      <c r="J95" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K95" s="5" t="s">
         <v>510</v>
-      </c>
-      <c r="J95" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K95" s="5" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="2:12">
@@ -8882,7 +8885,7 @@
         <v>2051</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E96" s="1">
         <v>1</v>
@@ -8894,16 +8897,16 @@
         <v>2</v>
       </c>
       <c r="H96" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I96" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="J96" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K96" s="5" t="s">
         <v>512</v>
-      </c>
-      <c r="J96" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K96" s="5" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="3:11">
@@ -8914,7 +8917,7 @@
         <v>2052</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E98" s="1">
         <v>1</v>
@@ -8926,16 +8929,16 @@
         <v>2</v>
       </c>
       <c r="H98" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I98" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="J98" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K98" s="6" t="s">
         <v>514</v>
-      </c>
-      <c r="J98" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K98" s="6" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="3:11">
@@ -8943,7 +8946,7 @@
         <v>2053</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E99" s="1">
         <v>1</v>
@@ -8955,16 +8958,16 @@
         <v>2</v>
       </c>
       <c r="H99" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I99" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="J99" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K99" s="6" t="s">
         <v>516</v>
-      </c>
-      <c r="J99" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K99" s="6" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="3:11">
@@ -8972,7 +8975,7 @@
         <v>2054</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E100" s="1">
         <v>1</v>
@@ -8984,16 +8987,16 @@
         <v>2</v>
       </c>
       <c r="H100" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I100" s="8" t="s">
+        <v>519</v>
+      </c>
+      <c r="J100" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K100" s="6" t="s">
         <v>518</v>
-      </c>
-      <c r="J100" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K100" s="6" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="3:11">
@@ -9001,7 +9004,7 @@
         <v>2055</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E101" s="1">
         <v>1</v>
@@ -9013,16 +9016,16 @@
         <v>2</v>
       </c>
       <c r="H101" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I101" s="8" t="s">
+        <v>521</v>
+      </c>
+      <c r="J101" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K101" s="6" t="s">
         <v>520</v>
-      </c>
-      <c r="J101" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K101" s="6" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="3:11">
@@ -9030,7 +9033,7 @@
         <v>2056</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E102" s="1">
         <v>1</v>
@@ -9042,16 +9045,16 @@
         <v>2</v>
       </c>
       <c r="H102" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I102" s="8" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="J102" s="8" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K102" s="6" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="3:11">
@@ -9059,7 +9062,7 @@
         <v>2057</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E103" s="1">
         <v>1</v>
@@ -9071,16 +9074,16 @@
         <v>2</v>
       </c>
       <c r="H103" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I103" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="J103" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K103" s="6" t="s">
         <v>523</v>
-      </c>
-      <c r="J103" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K103" s="6" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="3:11">
@@ -9088,7 +9091,7 @@
         <v>2058</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E104" s="1">
         <v>1</v>
@@ -9100,16 +9103,16 @@
         <v>2</v>
       </c>
       <c r="H104" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I104" s="8" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="J104" s="8" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K104" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="3:11">
@@ -9117,7 +9120,7 @@
         <v>2059</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E105" s="1">
         <v>1</v>
@@ -9129,16 +9132,16 @@
         <v>2</v>
       </c>
       <c r="H105" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I105" s="8" t="s">
+        <v>527</v>
+      </c>
+      <c r="J105" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K105" s="6" t="s">
         <v>526</v>
-      </c>
-      <c r="J105" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K105" s="6" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="3:11">
@@ -9146,7 +9149,7 @@
         <v>2060</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E106" s="1">
         <v>1</v>
@@ -9158,16 +9161,16 @@
         <v>2</v>
       </c>
       <c r="H106" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I106" s="8" t="s">
+        <v>529</v>
+      </c>
+      <c r="J106" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K106" s="6" t="s">
         <v>528</v>
-      </c>
-      <c r="J106" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K106" s="6" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="3:11">
@@ -9175,7 +9178,7 @@
         <v>2061</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E107" s="1">
         <v>1</v>
@@ -9187,16 +9190,16 @@
         <v>2</v>
       </c>
       <c r="H107" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I107" s="8" t="s">
+        <v>531</v>
+      </c>
+      <c r="J107" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K107" s="6" t="s">
         <v>530</v>
-      </c>
-      <c r="J107" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K107" s="6" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="108" customHeight="1" spans="3:11">
@@ -9204,7 +9207,7 @@
         <v>2062</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E108" s="1">
         <v>1</v>
@@ -9216,16 +9219,16 @@
         <v>2</v>
       </c>
       <c r="H108" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I108" s="8" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="J108" s="8" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K108" s="6" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="109" customHeight="1" spans="3:11">
@@ -9236,7 +9239,7 @@
         <v>2063</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E110" s="1">
         <v>1</v>
@@ -9248,16 +9251,16 @@
         <v>2</v>
       </c>
       <c r="H110" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I110" s="8" t="s">
+        <v>534</v>
+      </c>
+      <c r="J110" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K110" s="6" t="s">
         <v>533</v>
-      </c>
-      <c r="J110" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K110" s="6" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="3:11">
@@ -9265,7 +9268,7 @@
         <v>2064</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E111" s="1">
         <v>1</v>
@@ -9277,16 +9280,16 @@
         <v>2</v>
       </c>
       <c r="H111" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I111" s="8" t="s">
+        <v>536</v>
+      </c>
+      <c r="J111" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K111" s="6" t="s">
         <v>535</v>
-      </c>
-      <c r="J111" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K111" s="6" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="112" customHeight="1" spans="3:11">
@@ -9294,7 +9297,7 @@
         <v>2065</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E112" s="1">
         <v>1</v>
@@ -9306,16 +9309,16 @@
         <v>2</v>
       </c>
       <c r="H112" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I112" s="8" t="s">
+        <v>538</v>
+      </c>
+      <c r="J112" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K112" s="6" t="s">
         <v>537</v>
-      </c>
-      <c r="J112" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K112" s="6" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="113" customHeight="1" spans="3:11">
@@ -9323,7 +9326,7 @@
         <v>2066</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E113" s="1">
         <v>1</v>
@@ -9335,16 +9338,16 @@
         <v>2</v>
       </c>
       <c r="H113" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I113" s="8" t="s">
+        <v>540</v>
+      </c>
+      <c r="J113" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K113" s="6" t="s">
         <v>539</v>
-      </c>
-      <c r="J113" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K113" s="6" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="114" customHeight="1" spans="3:11">
@@ -9352,7 +9355,7 @@
         <v>2067</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E114" s="1">
         <v>1</v>
@@ -9364,16 +9367,16 @@
         <v>2</v>
       </c>
       <c r="H114" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I114" s="8" t="s">
+        <v>542</v>
+      </c>
+      <c r="J114" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K114" s="6" t="s">
         <v>541</v>
-      </c>
-      <c r="J114" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K114" s="6" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="115" customHeight="1" spans="3:11">
@@ -9381,7 +9384,7 @@
         <v>2068</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E115" s="1">
         <v>1</v>
@@ -9393,16 +9396,16 @@
         <v>2</v>
       </c>
       <c r="H115" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I115" s="8" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="J115" s="8" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K115" s="6" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="116" customHeight="1" spans="3:11">
@@ -9410,7 +9413,7 @@
         <v>2069</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E116" s="1">
         <v>1</v>
@@ -9422,16 +9425,16 @@
         <v>2</v>
       </c>
       <c r="H116" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I116" s="8" t="s">
+        <v>545</v>
+      </c>
+      <c r="J116" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K116" s="6" t="s">
         <v>544</v>
-      </c>
-      <c r="J116" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K116" s="6" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="117" customHeight="1" spans="3:11">
@@ -9439,7 +9442,7 @@
         <v>2070</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E117" s="1">
         <v>1</v>
@@ -9451,16 +9454,16 @@
         <v>2</v>
       </c>
       <c r="H117" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I117" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="J117" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K117" s="6" t="s">
         <v>546</v>
-      </c>
-      <c r="J117" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K117" s="6" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="118" customHeight="1" spans="3:11">
@@ -9468,7 +9471,7 @@
         <v>2071</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E118" s="1">
         <v>1</v>
@@ -9480,16 +9483,16 @@
         <v>2</v>
       </c>
       <c r="H118" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I118" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="J118" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="K118" s="6" t="s">
         <v>548</v>
-      </c>
-      <c r="J118" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="K118" s="6" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="119" customHeight="1" spans="3:11">
@@ -9497,7 +9500,7 @@
         <v>2072</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E119" s="1">
         <v>1</v>
@@ -9509,16 +9512,16 @@
         <v>2</v>
       </c>
       <c r="H119" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I119" s="8" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="J119" s="8" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K119" s="6" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="120" customHeight="1" spans="3:11">
